--- a/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电模型_参数与血缘_v4.3.xlsx
+++ b/业务/换电/定量计算/换电战略决策模型_v4_3/outputs/换电模型_参数与血缘_v4.3.xlsx
@@ -544,7 +544,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02_结果总表　　56 个输出结果，每个都标出「决定它的三个参数」。</t>
+          <t>02_结果总表　　57 个输出结果，每个都标出「决定它的三个参数」。</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6866,11 +6866,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>装机GWh / 最新储能装机</t>
+          <t>站内装机GWh / 最新储能装机</t>
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>107.94</v>
+        <v>6.29</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>national_battery_market.storage_install_gwh_2025 -0.91；0.swap_penetration +0.76；heavy.nev_rates +0.47</t>
+          <t>national_battery_market.storage_install_gwh_2025 -0.91；heavy.nev_rates +0.65；qiji75_trunk.inventory_blocks +0.62</t>
         </is>
       </c>
     </row>
@@ -6891,11 +6891,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>装机GWh / 2030储能装机预测</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="C39" s="11" t="n">
-        <v>48.57</v>
+        <v>2.83</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>national_battery_market.storage_install_gwh_2030 -0.91；0.swap_penetration +0.76；heavy.nev_rates +0.47</t>
+          <t>national_battery_market.storage_install_gwh_2030 -0.92；heavy.nev_rates +0.64；qiji75_trunk.inventory_blocks +0.64</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7294,7 @@
           <t>峰值年</t>
         </is>
       </c>
-      <c r="C55" s="11" t="n">
+      <c r="C55" s="7" t="n">
         <v>2030</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -7311,25 +7311,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>⑥资金</t>
+          <t>③资本</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>换电出资峰值/CFO</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="n">
-        <v>0.08024040040331126</v>
+          <t>外部股权融资（合资方出资）</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>1031.349999241995</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>倍</t>
+          <t>亿元</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>finance.debt_ratio -1.50；group_funding.projected_group_cfo_yi -1.46；finance.construction_ownership +1.00</t>
+          <t>finance.debt_ratio -1.50；battery_price_curve.platform_end_year +1.38；battery_price_curve.base_price_rmb_kwh +0.92</t>
         </is>
       </c>
     </row>
@@ -7341,20 +7341,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2030期末可动用资金</t>
+          <t>换电出资峰值/CFO</t>
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>8593.75294231216</v>
+        <v>0.08024040040331126</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>倍</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>group_funding.projected_group_cfo_yi +1.06；group_funding.initial_cash_and_trading_assets_yi +0.51；group_funding.projected_group_net_profit_yi -0.39</t>
+          <t>finance.debt_ratio -1.50；group_funding.projected_group_cfo_yi -1.46；finance.construction_ownership +1.00</t>
         </is>
       </c>
     </row>
@@ -7366,18 +7366,43 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
+          <t>2030期末可动用资金</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>8593.75294231216</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>group_funding.projected_group_cfo_yi +1.06；group_funding.initial_cash_and_trading_assets_yi +0.51；group_funding.projected_group_net_profit_yi -0.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>⑥资金</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>待决战略敞口</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="C59" t="n">
         <v>1770</v>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>亿元</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>solid_state.full_newbuild_capex_yi +0.42；storage_aidc.assumed_reuse_rate -0.27；storage_aidc.full_newbuild_capex_yi +0.18</t>
         </is>
@@ -7394,7 +7419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG205"/>
+  <dimension ref="A1:BH205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -7456,6 +7481,7 @@
     <col width="13" customWidth="1" min="57" max="57"/>
     <col width="13" customWidth="1" min="58" max="58"/>
     <col width="13" customWidth="1" min="59" max="59"/>
+    <col width="13" customWidth="1" min="60" max="60"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7651,12 +7677,12 @@
       </c>
       <c r="AM1" s="3" t="inlineStr">
         <is>
-          <t>装机GWh / 最新储能装机</t>
+          <t>站内装机GWh / 最新储能装机</t>
         </is>
       </c>
       <c r="AN1" s="3" t="inlineStr">
         <is>
-          <t>装机GWh / 2030储能装机预测</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="AO1" s="3" t="inlineStr">
@@ -7741,15 +7767,20 @@
       </c>
       <c r="BE1" s="3" t="inlineStr">
         <is>
+          <t>外部股权融资（合资方出资）</t>
+        </is>
+      </c>
+      <c r="BF1" s="3" t="inlineStr">
+        <is>
           <t>换电出资峰值/CFO</t>
         </is>
       </c>
-      <c r="BF1" s="3" t="inlineStr">
+      <c r="BG1" s="3" t="inlineStr">
         <is>
           <t>2030期末可动用资金</t>
         </is>
       </c>
-      <c r="BG1" s="3" t="inlineStr">
+      <c r="BH1" s="3" t="inlineStr">
         <is>
           <t>待决战略敞口</t>
         </is>
@@ -7936,6 +7967,9 @@
       <c r="BG3" t="n">
         <v>0</v>
       </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8117,6 +8151,9 @@
       <c r="BG4" t="n">
         <v>0</v>
       </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8290,12 +8327,15 @@
         <v>0</v>
       </c>
       <c r="BE5" t="n">
+        <v>-0.667</v>
+      </c>
+      <c r="BF5" t="n">
         <v>1</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BG5" t="n">
         <v>-0.052</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BH5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8479,6 +8519,9 @@
       <c r="BG6" t="n">
         <v>0</v>
       </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8660,6 +8703,9 @@
       <c r="BG7" t="n">
         <v>0</v>
       </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8781,10 +8827,10 @@
         <v>0.307</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.467</v>
+        <v>0.652</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.467</v>
+        <v>0.636</v>
       </c>
       <c r="AO8" t="n">
         <v>0.64</v>
@@ -8835,12 +8881,15 @@
         <v>0</v>
       </c>
       <c r="BE8" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="BF8" t="n">
         <v>0.39</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BG8" t="n">
         <v>-0.027</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BH8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8962,10 +9011,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.764</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.764</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0.112</v>
@@ -9016,12 +9065,15 @@
         <v>0</v>
       </c>
       <c r="BE9" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="BF9" t="n">
         <v>0.573</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BG9" t="n">
         <v>-0.031</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BH9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9143,10 +9195,10 @@
         <v>0.155</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.23</v>
+        <v>0.334</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.231</v>
+        <v>0.318</v>
       </c>
       <c r="AO10" t="n">
         <v>0.332</v>
@@ -9197,12 +9249,15 @@
         <v>0</v>
       </c>
       <c r="BE10" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="BF10" t="n">
         <v>0.188</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BG10" t="n">
         <v>-0.013</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BH10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9324,10 +9379,10 @@
         <v>0.126</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.176</v>
+        <v>0.27</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.177</v>
+        <v>0.283</v>
       </c>
       <c r="AO11" t="n">
         <v>0.27</v>
@@ -9378,12 +9433,15 @@
         <v>0</v>
       </c>
       <c r="BE11" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="BF11" t="n">
         <v>0.148</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BG11" t="n">
         <v>-0.012</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BH11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9505,10 +9563,10 @@
         <v>0.155</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.23</v>
+        <v>0.334</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.231</v>
+        <v>0.318</v>
       </c>
       <c r="AO12" t="n">
         <v>0.332</v>
@@ -9559,12 +9617,15 @@
         <v>0</v>
       </c>
       <c r="BE12" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="BF12" t="n">
         <v>0.188</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BG12" t="n">
         <v>-0.013</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BH12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9686,10 +9747,10 @@
         <v>0.126</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.176</v>
+        <v>0.27</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.177</v>
+        <v>0.283</v>
       </c>
       <c r="AO13" t="n">
         <v>0.27</v>
@@ -9740,12 +9801,15 @@
         <v>0</v>
       </c>
       <c r="BE13" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="BF13" t="n">
         <v>0.148</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BG13" t="n">
         <v>-0.012</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BH13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9867,10 +9931,10 @@
         <v>0.331</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.184</v>
+        <v>0.191</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.185</v>
+        <v>0.212</v>
       </c>
       <c r="AO14" t="n">
         <v>0.174</v>
@@ -9921,12 +9985,15 @@
         <v>0</v>
       </c>
       <c r="BE14" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BF14" t="n">
         <v>0.126</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BG14" t="n">
         <v>-0.008999999999999999</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BH14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10050,10 +10117,10 @@
         <v>0.331</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.184</v>
+        <v>0.191</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.185</v>
+        <v>0.212</v>
       </c>
       <c r="AO15" t="n">
         <v>0.174</v>
@@ -10104,12 +10171,15 @@
         <v>0</v>
       </c>
       <c r="BE15" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BF15" t="n">
         <v>0.126</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BG15" t="n">
         <v>-0.008999999999999999</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BH15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10231,10 +10301,10 @@
         <v>0.331</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.184</v>
+        <v>0.191</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.185</v>
+        <v>0.212</v>
       </c>
       <c r="AO16" t="n">
         <v>0.174</v>
@@ -10285,12 +10355,15 @@
         <v>0</v>
       </c>
       <c r="BE16" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BF16" t="n">
         <v>0.126</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BG16" t="n">
         <v>-0.008999999999999999</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BH16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10469,9 +10542,12 @@
         <v>-1.5</v>
       </c>
       <c r="BF17" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BG17" t="n">
         <v>0.078</v>
       </c>
-      <c r="BG17" t="n">
+      <c r="BH17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10655,6 +10731,9 @@
       <c r="BG18" t="n">
         <v>0</v>
       </c>
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10836,6 +10915,9 @@
       <c r="BG19" t="n">
         <v>0</v>
       </c>
+      <c r="BH19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10955,10 +11037,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.126</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.126</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0.018</v>
@@ -11009,12 +11091,15 @@
         <v>0</v>
       </c>
       <c r="BE20" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="BF20" t="n">
         <v>0.094</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BG20" t="n">
         <v>-0.005</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BH20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11138,10 +11223,10 @@
         <v>0.222</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.074</v>
+        <v>0.095</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.074</v>
+        <v>0.106</v>
       </c>
       <c r="AO21" t="n">
         <v>0.081</v>
@@ -11192,12 +11277,15 @@
         <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>0.068</v>
       </c>
       <c r="BF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG21" t="n">
         <v>-0.004</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BH21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11319,10 +11407,10 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.126</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.126</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0.018</v>
@@ -11373,12 +11461,15 @@
         <v>0</v>
       </c>
       <c r="BE22" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="BF22" t="n">
         <v>0.094</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BG22" t="n">
         <v>-0.005</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BH22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11500,10 +11591,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0.013</v>
@@ -11554,12 +11645,15 @@
         <v>0</v>
       </c>
       <c r="BE23" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="BF23" t="n">
         <v>0.066</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BG23" t="n">
         <v>-0.004</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BH23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11743,6 +11837,9 @@
       <c r="BG24" t="n">
         <v>0</v>
       </c>
+      <c r="BH24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11916,12 +12013,15 @@
         <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.384</v>
       </c>
       <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
         <v>-0.015</v>
       </c>
-      <c r="BG25" t="n">
+      <c r="BH25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12043,10 +12143,10 @@
         <v>0.016</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.073</v>
+        <v>0.032</v>
       </c>
       <c r="AN26" t="n">
-        <v>0.074</v>
+        <v>0.035</v>
       </c>
       <c r="AO26" t="n">
         <v>0.016</v>
@@ -12097,12 +12197,15 @@
         <v>0</v>
       </c>
       <c r="BE26" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="BF26" t="n">
         <v>0.054</v>
       </c>
-      <c r="BF26" t="n">
+      <c r="BG26" t="n">
         <v>-0.003</v>
       </c>
-      <c r="BG26" t="n">
+      <c r="BH26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12224,10 +12327,10 @@
         <v>0.134</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.06</v>
+        <v>0.064</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.062</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AO27" t="n">
         <v>0.049</v>
@@ -12278,12 +12381,15 @@
         <v>0</v>
       </c>
       <c r="BE27" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BF27" t="n">
         <v>0.048</v>
       </c>
-      <c r="BF27" t="n">
+      <c r="BG27" t="n">
         <v>-0.003</v>
       </c>
-      <c r="BG27" t="n">
+      <c r="BH27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12405,10 +12511,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0.013</v>
@@ -12459,12 +12565,15 @@
         <v>0</v>
       </c>
       <c r="BE28" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="BF28" t="n">
         <v>0.066</v>
       </c>
-      <c r="BF28" t="n">
+      <c r="BG28" t="n">
         <v>-0.004</v>
       </c>
-      <c r="BG28" t="n">
+      <c r="BH28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12640,12 +12749,15 @@
         <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>-0.629</v>
       </c>
       <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
         <v>0.007</v>
       </c>
-      <c r="BG29" t="n">
+      <c r="BH29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12767,10 +12879,10 @@
         <v>-0.1</v>
       </c>
       <c r="AM30" t="n">
-        <v>-0.045</v>
+        <v>-0.032</v>
       </c>
       <c r="AN30" t="n">
-        <v>-0.045</v>
+        <v>-0.035</v>
       </c>
       <c r="AO30" t="n">
         <v>-0.037</v>
@@ -12821,12 +12933,15 @@
         <v>0</v>
       </c>
       <c r="BE30" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="BF30" t="n">
         <v>-0.036</v>
       </c>
-      <c r="BF30" t="n">
+      <c r="BG30" t="n">
         <v>0.002</v>
       </c>
-      <c r="BG30" t="n">
+      <c r="BH30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13010,6 +13125,9 @@
       <c r="BG31" t="n">
         <v>0</v>
       </c>
+      <c r="BH31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -13129,10 +13247,10 @@
         <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>0.636</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -13183,12 +13301,15 @@
         <v>0</v>
       </c>
       <c r="BE32" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="BF32" t="n">
         <v>0.037</v>
       </c>
-      <c r="BF32" t="n">
+      <c r="BG32" t="n">
         <v>-0.001</v>
       </c>
-      <c r="BG32" t="n">
+      <c r="BH32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13310,10 +13431,10 @@
         <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>0.636</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -13364,12 +13485,15 @@
         <v>0</v>
       </c>
       <c r="BE33" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="BF33" t="n">
         <v>0.037</v>
       </c>
-      <c r="BF33" t="n">
+      <c r="BG33" t="n">
         <v>-0.001</v>
       </c>
-      <c r="BG33" t="n">
+      <c r="BH33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13491,10 +13615,10 @@
         <v>0.08</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.027</v>
+        <v>0.035</v>
       </c>
       <c r="AO34" t="n">
         <v>0.029</v>
@@ -13545,12 +13669,15 @@
         <v>0</v>
       </c>
       <c r="BE34" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="BF34" t="n">
         <v>0.021</v>
       </c>
-      <c r="BF34" t="n">
+      <c r="BG34" t="n">
         <v>-0.001</v>
       </c>
-      <c r="BG34" t="n">
+      <c r="BH34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13674,10 +13801,10 @@
         <v>0.08</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
       <c r="AN35" t="n">
-        <v>0.027</v>
+        <v>0.035</v>
       </c>
       <c r="AO35" t="n">
         <v>0.029</v>
@@ -13728,12 +13855,15 @@
         <v>0</v>
       </c>
       <c r="BE35" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="BF35" t="n">
         <v>0.021</v>
       </c>
-      <c r="BF35" t="n">
+      <c r="BG35" t="n">
         <v>-0.001</v>
       </c>
-      <c r="BG35" t="n">
+      <c r="BH35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13855,10 +13985,10 @@
         <v>0.08</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
       <c r="AN36" t="n">
-        <v>0.027</v>
+        <v>0.035</v>
       </c>
       <c r="AO36" t="n">
         <v>0.029</v>
@@ -13909,12 +14039,15 @@
         <v>0</v>
       </c>
       <c r="BE36" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="BF36" t="n">
         <v>0.021</v>
       </c>
-      <c r="BF36" t="n">
+      <c r="BG36" t="n">
         <v>-0.001</v>
       </c>
-      <c r="BG36" t="n">
+      <c r="BH36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14036,10 +14169,10 @@
         <v>0.08</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
       <c r="AN37" t="n">
-        <v>0.027</v>
+        <v>0.035</v>
       </c>
       <c r="AO37" t="n">
         <v>0.029</v>
@@ -14090,12 +14223,15 @@
         <v>0</v>
       </c>
       <c r="BE37" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="BF37" t="n">
         <v>0.021</v>
       </c>
-      <c r="BF37" t="n">
+      <c r="BG37" t="n">
         <v>-0.001</v>
       </c>
-      <c r="BG37" t="n">
+      <c r="BH37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14217,10 +14353,10 @@
         <v>0.052</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.024</v>
+        <v>0.016</v>
       </c>
       <c r="AN38" t="n">
-        <v>0.025</v>
+        <v>0.035</v>
       </c>
       <c r="AO38" t="n">
         <v>0.019</v>
@@ -14271,12 +14407,15 @@
         <v>0</v>
       </c>
       <c r="BE38" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BF38" t="n">
         <v>0.019</v>
       </c>
-      <c r="BF38" t="n">
+      <c r="BG38" t="n">
         <v>-0.001</v>
       </c>
-      <c r="BG38" t="n">
+      <c r="BH38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14398,10 +14537,10 @@
         <v>-0.07099999999999999</v>
       </c>
       <c r="AM39" t="n">
-        <v>-0.023</v>
+        <v>-0.032</v>
       </c>
       <c r="AN39" t="n">
-        <v>-0.023</v>
+        <v>-0.035</v>
       </c>
       <c r="AO39" t="n">
         <v>-0.026</v>
@@ -14452,12 +14591,15 @@
         <v>0</v>
       </c>
       <c r="BE39" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="BF39" t="n">
         <v>-0.019</v>
       </c>
-      <c r="BF39" t="n">
+      <c r="BG39" t="n">
         <v>0.001</v>
       </c>
-      <c r="BG39" t="n">
+      <c r="BH39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14641,6 +14783,9 @@
       <c r="BG40" t="n">
         <v>0</v>
       </c>
+      <c r="BH40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -14762,10 +14907,10 @@
         <v>0.052</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.024</v>
+        <v>0.016</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.025</v>
+        <v>0.035</v>
       </c>
       <c r="AO41" t="n">
         <v>0.019</v>
@@ -14816,12 +14961,15 @@
         <v>0</v>
       </c>
       <c r="BE41" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BF41" t="n">
         <v>0.019</v>
       </c>
-      <c r="BF41" t="n">
+      <c r="BG41" t="n">
         <v>-0.001</v>
       </c>
-      <c r="BG41" t="n">
+      <c r="BH41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14943,10 +15091,10 @@
         <v>0.052</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.024</v>
+        <v>0.016</v>
       </c>
       <c r="AN42" t="n">
-        <v>0.025</v>
+        <v>0.035</v>
       </c>
       <c r="AO42" t="n">
         <v>0.019</v>
@@ -14997,12 +15145,15 @@
         <v>0</v>
       </c>
       <c r="BE42" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BF42" t="n">
         <v>0.019</v>
       </c>
-      <c r="BF42" t="n">
+      <c r="BG42" t="n">
         <v>-0.001</v>
       </c>
-      <c r="BG42" t="n">
+      <c r="BH42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15124,10 +15275,10 @@
         <v>0.016</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.073</v>
+        <v>0.032</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.074</v>
+        <v>0.035</v>
       </c>
       <c r="AO43" t="n">
         <v>0.016</v>
@@ -15178,12 +15329,15 @@
         <v>0</v>
       </c>
       <c r="BE43" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="BF43" t="n">
         <v>0.054</v>
       </c>
-      <c r="BF43" t="n">
+      <c r="BG43" t="n">
         <v>-0.003</v>
       </c>
-      <c r="BG43" t="n">
+      <c r="BH43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15305,10 +15459,10 @@
         <v>0.052</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.024</v>
+        <v>0.016</v>
       </c>
       <c r="AN44" t="n">
-        <v>0.025</v>
+        <v>0.035</v>
       </c>
       <c r="AO44" t="n">
         <v>0.019</v>
@@ -15359,12 +15513,15 @@
         <v>0</v>
       </c>
       <c r="BE44" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BF44" t="n">
         <v>0.019</v>
       </c>
-      <c r="BF44" t="n">
+      <c r="BG44" t="n">
         <v>-0.001</v>
       </c>
-      <c r="BG44" t="n">
+      <c r="BH44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15486,10 +15643,10 @@
         <v>-0.049</v>
       </c>
       <c r="AM45" t="n">
-        <v>-0.022</v>
+        <v>-0.016</v>
       </c>
       <c r="AN45" t="n">
-        <v>-0.021</v>
+        <v>0</v>
       </c>
       <c r="AO45" t="n">
         <v>-0.018</v>
@@ -15540,12 +15697,15 @@
         <v>0</v>
       </c>
       <c r="BE45" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="BF45" t="n">
         <v>-0.017</v>
       </c>
-      <c r="BF45" t="n">
+      <c r="BG45" t="n">
         <v>0.001</v>
       </c>
-      <c r="BG45" t="n">
+      <c r="BH45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15729,6 +15889,9 @@
       <c r="BG46" t="n">
         <v>0</v>
       </c>
+      <c r="BH46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -15910,6 +16073,9 @@
       <c r="BG47" t="n">
         <v>0</v>
       </c>
+      <c r="BH47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -16029,10 +16195,10 @@
         <v>-0.022</v>
       </c>
       <c r="AM48" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AO48" t="n">
         <v>-0.008999999999999999</v>
@@ -16086,9 +16252,12 @@
         <v>-0.008</v>
       </c>
       <c r="BF48" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="BG48" t="n">
         <v>0.001</v>
       </c>
-      <c r="BG48" t="n">
+      <c r="BH48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16210,10 +16379,10 @@
         <v>-0.022</v>
       </c>
       <c r="AM49" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AO49" t="n">
         <v>-0.008999999999999999</v>
@@ -16267,9 +16436,12 @@
         <v>-0.008</v>
       </c>
       <c r="BF49" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="BG49" t="n">
         <v>0.001</v>
       </c>
-      <c r="BG49" t="n">
+      <c r="BH49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16445,12 +16617,15 @@
         <v>0</v>
       </c>
       <c r="BE50" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="BF50" t="n">
         <v>0.075</v>
       </c>
-      <c r="BF50" t="n">
+      <c r="BG50" t="n">
         <v>-0.003</v>
       </c>
-      <c r="BG50" t="n">
+      <c r="BH50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16572,10 +16747,10 @@
         <v>0</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
@@ -16626,12 +16801,15 @@
         <v>0</v>
       </c>
       <c r="BE51" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="BF51" t="n">
         <v>0.02</v>
       </c>
-      <c r="BF51" t="n">
+      <c r="BG51" t="n">
         <v>-0</v>
       </c>
-      <c r="BG51" t="n">
+      <c r="BH51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16753,10 +16931,10 @@
         <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>0.141</v>
       </c>
       <c r="AO52" t="n">
         <v>0</v>
@@ -16807,12 +16985,15 @@
         <v>0</v>
       </c>
       <c r="BE52" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="BF52" t="n">
         <v>0.02</v>
       </c>
-      <c r="BF52" t="n">
+      <c r="BG52" t="n">
         <v>-0</v>
       </c>
-      <c r="BG52" t="n">
+      <c r="BH52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16996,6 +17177,9 @@
       <c r="BG53" t="n">
         <v>0</v>
       </c>
+      <c r="BH53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -17177,6 +17361,9 @@
       <c r="BG54" t="n">
         <v>0</v>
       </c>
+      <c r="BH54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -17358,6 +17545,9 @@
       <c r="BG55" t="n">
         <v>0</v>
       </c>
+      <c r="BH55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17539,6 +17729,9 @@
       <c r="BG56" t="n">
         <v>0</v>
       </c>
+      <c r="BH56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17658,10 +17851,10 @@
         <v>0</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>0.191</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>0.212</v>
       </c>
       <c r="AO57" t="n">
         <v>0</v>
@@ -17712,12 +17905,15 @@
         <v>0</v>
       </c>
       <c r="BE57" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="BF57" t="n">
         <v>0.002</v>
       </c>
-      <c r="BF57" t="n">
+      <c r="BG57" t="n">
         <v>-0</v>
       </c>
-      <c r="BG57" t="n">
+      <c r="BH57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17839,10 +18035,10 @@
         <v>0</v>
       </c>
       <c r="AM58" t="n">
-        <v>0</v>
+        <v>0.191</v>
       </c>
       <c r="AN58" t="n">
-        <v>0</v>
+        <v>0.212</v>
       </c>
       <c r="AO58" t="n">
         <v>0</v>
@@ -17893,12 +18089,15 @@
         <v>0</v>
       </c>
       <c r="BE58" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="BF58" t="n">
         <v>0.002</v>
       </c>
-      <c r="BF58" t="n">
+      <c r="BG58" t="n">
         <v>-0</v>
       </c>
-      <c r="BG58" t="n">
+      <c r="BH58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18074,12 +18273,15 @@
         <v>0</v>
       </c>
       <c r="BE59" t="n">
-        <v>0</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="BF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG59" t="n">
         <v>0.001</v>
       </c>
-      <c r="BG59" t="n">
+      <c r="BH59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18263,6 +18465,9 @@
       <c r="BG60" t="n">
         <v>0</v>
       </c>
+      <c r="BH60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -18382,10 +18587,10 @@
         <v>-0.298</v>
       </c>
       <c r="AM61" t="n">
-        <v>0</v>
+        <v>-0.175</v>
       </c>
       <c r="AN61" t="n">
-        <v>0</v>
+        <v>-0.177</v>
       </c>
       <c r="AO61" t="n">
         <v>0</v>
@@ -18436,12 +18641,15 @@
         <v>0</v>
       </c>
       <c r="BE61" t="n">
-        <v>0</v>
+        <v>-0.021</v>
       </c>
       <c r="BF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG61" t="n">
         <v>0.002</v>
       </c>
-      <c r="BG61" t="n">
+      <c r="BH61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18617,12 +18825,15 @@
         <v>0</v>
       </c>
       <c r="BE62" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="BF62" t="n">
         <v>0.08699999999999999</v>
       </c>
-      <c r="BF62" t="n">
+      <c r="BG62" t="n">
         <v>-0.001</v>
       </c>
-      <c r="BG62" t="n">
+      <c r="BH62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18798,12 +19009,15 @@
         <v>0</v>
       </c>
       <c r="BE63" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="BF63" t="n">
         <v>0.007</v>
       </c>
-      <c r="BF63" t="n">
+      <c r="BG63" t="n">
         <v>-0.001</v>
       </c>
-      <c r="BG63" t="n">
+      <c r="BH63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18925,10 +19139,10 @@
         <v>-0.321</v>
       </c>
       <c r="AM64" t="n">
-        <v>0</v>
+        <v>-0.127</v>
       </c>
       <c r="AN64" t="n">
-        <v>0</v>
+        <v>-0.141</v>
       </c>
       <c r="AO64" t="n">
         <v>0</v>
@@ -18979,12 +19193,15 @@
         <v>0</v>
       </c>
       <c r="BE64" t="n">
-        <v>0</v>
+        <v>-0.021</v>
       </c>
       <c r="BF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG64" t="n">
         <v>0.002</v>
       </c>
-      <c r="BG64" t="n">
+      <c r="BH64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19160,12 +19377,15 @@
         <v>0</v>
       </c>
       <c r="BE65" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="BF65" t="n">
         <v>0.825</v>
       </c>
-      <c r="BF65" t="n">
+      <c r="BG65" t="n">
         <v>-0.047</v>
       </c>
-      <c r="BG65" t="n">
+      <c r="BH65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19349,6 +19569,9 @@
       <c r="BG66" t="n">
         <v>0</v>
       </c>
+      <c r="BH66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -19530,6 +19753,9 @@
       <c r="BG67" t="n">
         <v>0</v>
       </c>
+      <c r="BH67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -19649,10 +19875,10 @@
         <v>0</v>
       </c>
       <c r="AM68" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="AN68" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AO68" t="n">
         <v>0</v>
@@ -19703,12 +19929,15 @@
         <v>0</v>
       </c>
       <c r="BE68" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="BF68" t="n">
         <v>0.003</v>
       </c>
-      <c r="BF68" t="n">
+      <c r="BG68" t="n">
         <v>-0</v>
       </c>
-      <c r="BG68" t="n">
+      <c r="BH68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19830,10 +20059,10 @@
         <v>0</v>
       </c>
       <c r="AM69" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="AN69" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AO69" t="n">
         <v>0</v>
@@ -19884,12 +20113,15 @@
         <v>0</v>
       </c>
       <c r="BE69" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="BF69" t="n">
         <v>0.003</v>
       </c>
-      <c r="BF69" t="n">
+      <c r="BG69" t="n">
         <v>-0</v>
       </c>
-      <c r="BG69" t="n">
+      <c r="BH69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20073,6 +20305,9 @@
       <c r="BG70" t="n">
         <v>0</v>
       </c>
+      <c r="BH70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -20254,6 +20489,9 @@
       <c r="BG71" t="n">
         <v>0</v>
       </c>
+      <c r="BH71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -20435,6 +20673,9 @@
       <c r="BG72" t="n">
         <v>0</v>
       </c>
+      <c r="BH72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -20608,12 +20849,15 @@
         <v>0</v>
       </c>
       <c r="BE73" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="BF73" t="n">
         <v>0.006</v>
       </c>
-      <c r="BF73" t="n">
+      <c r="BG73" t="n">
         <v>-0</v>
       </c>
-      <c r="BG73" t="n">
+      <c r="BH73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20797,6 +21041,9 @@
       <c r="BG74" t="n">
         <v>0</v>
       </c>
+      <c r="BH74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -20978,6 +21225,9 @@
       <c r="BG75" t="n">
         <v>0</v>
       </c>
+      <c r="BH75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -21159,6 +21409,9 @@
       <c r="BG76" t="n">
         <v>0</v>
       </c>
+      <c r="BH76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -21332,12 +21585,15 @@
         <v>0</v>
       </c>
       <c r="BE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF77" t="n">
         <v>0.175</v>
       </c>
-      <c r="BF77" t="n">
+      <c r="BG77" t="n">
         <v>-0</v>
       </c>
-      <c r="BG77" t="n">
+      <c r="BH77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21521,6 +21777,9 @@
       <c r="BG78" t="n">
         <v>0</v>
       </c>
+      <c r="BH78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -21702,6 +21961,9 @@
       <c r="BG79" t="n">
         <v>0</v>
       </c>
+      <c r="BH79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -21883,6 +22145,9 @@
       <c r="BG80" t="n">
         <v>0</v>
       </c>
+      <c r="BH80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -22056,12 +22321,15 @@
         <v>0</v>
       </c>
       <c r="BE81" t="n">
-        <v>0</v>
+        <v>-0.196</v>
       </c>
       <c r="BF81" t="n">
         <v>0</v>
       </c>
       <c r="BG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22245,6 +22513,9 @@
       <c r="BG82" t="n">
         <v>0</v>
       </c>
+      <c r="BH82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -22428,6 +22699,9 @@
       <c r="BG83" t="n">
         <v>0</v>
       </c>
+      <c r="BH83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -22609,6 +22883,9 @@
       <c r="BG84" t="n">
         <v>0</v>
       </c>
+      <c r="BH84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -22790,6 +23067,9 @@
       <c r="BG85" t="n">
         <v>0</v>
       </c>
+      <c r="BH85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -22971,6 +23251,9 @@
       <c r="BG86" t="n">
         <v>0</v>
       </c>
+      <c r="BH86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -23152,6 +23435,9 @@
       <c r="BG87" t="n">
         <v>0</v>
       </c>
+      <c r="BH87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -23333,6 +23619,9 @@
       <c r="BG88" t="n">
         <v>0</v>
       </c>
+      <c r="BH88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -23514,6 +23803,9 @@
       <c r="BG89" t="n">
         <v>0</v>
       </c>
+      <c r="BH89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -23695,6 +23987,9 @@
       <c r="BG90" t="n">
         <v>0</v>
       </c>
+      <c r="BH90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -23876,6 +24171,9 @@
       <c r="BG91" t="n">
         <v>0</v>
       </c>
+      <c r="BH91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -24057,6 +24355,9 @@
       <c r="BG92" t="n">
         <v>0</v>
       </c>
+      <c r="BH92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -24238,6 +24539,9 @@
       <c r="BG93" t="n">
         <v>0</v>
       </c>
+      <c r="BH93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -24419,6 +24723,9 @@
       <c r="BG94" t="n">
         <v>0</v>
       </c>
+      <c r="BH94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -24600,6 +24907,9 @@
       <c r="BG95" t="n">
         <v>0</v>
       </c>
+      <c r="BH95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -24781,6 +25091,9 @@
       <c r="BG96" t="n">
         <v>0</v>
       </c>
+      <c r="BH96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -24962,6 +25275,9 @@
       <c r="BG97" t="n">
         <v>0</v>
       </c>
+      <c r="BH97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -25143,6 +25459,9 @@
       <c r="BG98" t="n">
         <v>0</v>
       </c>
+      <c r="BH98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -25324,6 +25643,9 @@
       <c r="BG99" t="n">
         <v>0</v>
       </c>
+      <c r="BH99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -25505,6 +25827,9 @@
       <c r="BG100" t="n">
         <v>0</v>
       </c>
+      <c r="BH100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -25686,6 +26011,9 @@
       <c r="BG101" t="n">
         <v>0</v>
       </c>
+      <c r="BH101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -25867,6 +26195,9 @@
       <c r="BG102" t="n">
         <v>0</v>
       </c>
+      <c r="BH102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -26048,6 +26379,9 @@
       <c r="BG103" t="n">
         <v>0</v>
       </c>
+      <c r="BH103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -26229,6 +26563,9 @@
       <c r="BG104" t="n">
         <v>0</v>
       </c>
+      <c r="BH104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -26410,6 +26747,9 @@
       <c r="BG105" t="n">
         <v>0</v>
       </c>
+      <c r="BH105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -26591,6 +26931,9 @@
       <c r="BG106" t="n">
         <v>0</v>
       </c>
+      <c r="BH106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -26772,6 +27115,9 @@
       <c r="BG107" t="n">
         <v>0</v>
       </c>
+      <c r="BH107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -26953,6 +27299,9 @@
       <c r="BG108" t="n">
         <v>0</v>
       </c>
+      <c r="BH108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -27134,6 +27483,9 @@
       <c r="BG109" t="n">
         <v>0</v>
       </c>
+      <c r="BH109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -27315,6 +27667,9 @@
       <c r="BG110" t="n">
         <v>0</v>
       </c>
+      <c r="BH110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -27496,6 +27851,9 @@
       <c r="BG111" t="n">
         <v>0</v>
       </c>
+      <c r="BH111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -27677,6 +28035,9 @@
       <c r="BG112" t="n">
         <v>0</v>
       </c>
+      <c r="BH112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -27858,6 +28219,9 @@
       <c r="BG113" t="n">
         <v>0</v>
       </c>
+      <c r="BH113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -27977,7 +28341,7 @@
         <v>0</v>
       </c>
       <c r="AM114" t="n">
-        <v>-0.909</v>
+        <v>-0.906</v>
       </c>
       <c r="AN114" t="n">
         <v>0</v>
@@ -28037,6 +28401,9 @@
         <v>0</v>
       </c>
       <c r="BG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH114" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28161,7 +28528,7 @@
         <v>0</v>
       </c>
       <c r="AN115" t="n">
-        <v>-0.908</v>
+        <v>-0.919</v>
       </c>
       <c r="AO115" t="n">
         <v>0</v>
@@ -28218,6 +28585,9 @@
         <v>0</v>
       </c>
       <c r="BG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH115" t="n">
         <v>0</v>
       </c>
     </row>
@@ -28401,6 +28771,9 @@
       <c r="BG116" t="n">
         <v>0</v>
       </c>
+      <c r="BH116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -28582,6 +28955,9 @@
       <c r="BG117" t="n">
         <v>0</v>
       </c>
+      <c r="BH117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -28763,6 +29139,9 @@
       <c r="BG118" t="n">
         <v>0</v>
       </c>
+      <c r="BH118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -28944,6 +29323,9 @@
       <c r="BG119" t="n">
         <v>0</v>
       </c>
+      <c r="BH119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -29125,6 +29507,9 @@
       <c r="BG120" t="n">
         <v>0</v>
       </c>
+      <c r="BH120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -29306,6 +29691,9 @@
       <c r="BG121" t="n">
         <v>0</v>
       </c>
+      <c r="BH121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -29487,6 +29875,9 @@
       <c r="BG122" t="n">
         <v>0</v>
       </c>
+      <c r="BH122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -29668,6 +30059,9 @@
       <c r="BG123" t="n">
         <v>0</v>
       </c>
+      <c r="BH123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -29849,6 +30243,9 @@
       <c r="BG124" t="n">
         <v>0</v>
       </c>
+      <c r="BH124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -30030,6 +30427,9 @@
       <c r="BG125" t="n">
         <v>0</v>
       </c>
+      <c r="BH125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -30211,6 +30611,9 @@
       <c r="BG126" t="n">
         <v>0</v>
       </c>
+      <c r="BH126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -30392,6 +30795,9 @@
       <c r="BG127" t="n">
         <v>0</v>
       </c>
+      <c r="BH127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -30573,6 +30979,9 @@
       <c r="BG128" t="n">
         <v>0</v>
       </c>
+      <c r="BH128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -30754,6 +31163,9 @@
       <c r="BG129" t="n">
         <v>0</v>
       </c>
+      <c r="BH129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -30935,6 +31347,9 @@
       <c r="BG130" t="n">
         <v>0</v>
       </c>
+      <c r="BH130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -31116,6 +31531,9 @@
       <c r="BG131" t="n">
         <v>0</v>
       </c>
+      <c r="BH131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -31297,6 +31715,9 @@
       <c r="BG132" t="n">
         <v>0</v>
       </c>
+      <c r="BH132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -31478,6 +31899,9 @@
       <c r="BG133" t="n">
         <v>0</v>
       </c>
+      <c r="BH133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -31659,6 +32083,9 @@
       <c r="BG134" t="n">
         <v>0</v>
       </c>
+      <c r="BH134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -31840,6 +32267,9 @@
       <c r="BG135" t="n">
         <v>0</v>
       </c>
+      <c r="BH135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -32021,6 +32451,9 @@
       <c r="BG136" t="n">
         <v>0</v>
       </c>
+      <c r="BH136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -32202,6 +32635,9 @@
       <c r="BG137" t="n">
         <v>0</v>
       </c>
+      <c r="BH137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -32383,6 +32819,9 @@
       <c r="BG138" t="n">
         <v>0</v>
       </c>
+      <c r="BH138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -32564,6 +33003,9 @@
       <c r="BG139" t="n">
         <v>0</v>
       </c>
+      <c r="BH139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -32747,6 +33189,9 @@
       <c r="BG140" t="n">
         <v>0</v>
       </c>
+      <c r="BH140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -32928,6 +33373,9 @@
       <c r="BG141" t="n">
         <v>0</v>
       </c>
+      <c r="BH141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -33101,12 +33549,15 @@
         <v>0</v>
       </c>
       <c r="BE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF142" t="n">
         <v>-0.054</v>
       </c>
-      <c r="BF142" t="n">
-        <v>0</v>
-      </c>
       <c r="BG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH142" t="n">
         <v>0</v>
       </c>
     </row>
@@ -33290,6 +33741,9 @@
       <c r="BG143" t="n">
         <v>0</v>
       </c>
+      <c r="BH143" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -33471,6 +33925,9 @@
       <c r="BG144" t="n">
         <v>0</v>
       </c>
+      <c r="BH144" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -33652,6 +34109,9 @@
       <c r="BG145" t="n">
         <v>0</v>
       </c>
+      <c r="BH145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -33833,6 +34293,9 @@
       <c r="BG146" t="n">
         <v>0</v>
       </c>
+      <c r="BH146" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -34014,6 +34477,9 @@
       <c r="BG147" t="n">
         <v>0</v>
       </c>
+      <c r="BH147" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -34195,6 +34661,9 @@
       <c r="BG148" t="n">
         <v>0</v>
       </c>
+      <c r="BH148" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -34376,6 +34845,9 @@
       <c r="BG149" t="n">
         <v>0</v>
       </c>
+      <c r="BH149" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -34557,6 +35029,9 @@
       <c r="BG150" t="n">
         <v>0</v>
       </c>
+      <c r="BH150" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -34730,12 +35205,15 @@
         <v>0</v>
       </c>
       <c r="BE151" t="n">
-        <v>0</v>
+        <v>-0.151</v>
       </c>
       <c r="BF151" t="n">
         <v>0</v>
       </c>
       <c r="BG151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH151" t="n">
         <v>0</v>
       </c>
     </row>
@@ -34911,12 +35389,15 @@
         <v>0</v>
       </c>
       <c r="BE152" t="n">
-        <v>0</v>
+        <v>-0.034</v>
       </c>
       <c r="BF152" t="n">
         <v>0</v>
       </c>
       <c r="BG152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH152" t="n">
         <v>0</v>
       </c>
     </row>
@@ -35092,12 +35573,15 @@
         <v>0</v>
       </c>
       <c r="BE153" t="n">
-        <v>0</v>
+        <v>-0.305</v>
       </c>
       <c r="BF153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG153" t="n">
         <v>0.003</v>
       </c>
-      <c r="BG153" t="n">
+      <c r="BH153" t="n">
         <v>0</v>
       </c>
     </row>
@@ -35273,12 +35757,15 @@
         <v>0</v>
       </c>
       <c r="BE154" t="n">
-        <v>0</v>
+        <v>-0.305</v>
       </c>
       <c r="BF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG154" t="n">
         <v>0.003</v>
       </c>
-      <c r="BG154" t="n">
+      <c r="BH154" t="n">
         <v>0</v>
       </c>
     </row>
@@ -35462,6 +35949,9 @@
       <c r="BG155" t="n">
         <v>0</v>
       </c>
+      <c r="BH155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -35635,12 +36125,15 @@
         <v>0</v>
       </c>
       <c r="BE156" t="n">
-        <v>0</v>
+        <v>-0.305</v>
       </c>
       <c r="BF156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG156" t="n">
         <v>0.003</v>
       </c>
-      <c r="BG156" t="n">
+      <c r="BH156" t="n">
         <v>0</v>
       </c>
     </row>
@@ -35824,6 +36317,9 @@
       <c r="BG157" t="n">
         <v>0</v>
       </c>
+      <c r="BH157" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -36005,6 +36501,9 @@
       <c r="BG158" t="n">
         <v>0</v>
       </c>
+      <c r="BH158" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -36186,6 +36685,9 @@
       <c r="BG159" t="n">
         <v>0</v>
       </c>
+      <c r="BH159" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -36367,6 +36869,9 @@
       <c r="BG160" t="n">
         <v>0</v>
       </c>
+      <c r="BH160" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -36548,6 +37053,9 @@
       <c r="BG161" t="n">
         <v>0</v>
       </c>
+      <c r="BH161" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -36729,6 +37237,9 @@
       <c r="BG162" t="n">
         <v>0</v>
       </c>
+      <c r="BH162" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -36910,6 +37421,9 @@
       <c r="BG163" t="n">
         <v>0</v>
       </c>
+      <c r="BH163" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -37091,6 +37605,9 @@
       <c r="BG164" t="n">
         <v>0</v>
       </c>
+      <c r="BH164" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -37272,6 +37789,9 @@
       <c r="BG165" t="n">
         <v>0</v>
       </c>
+      <c r="BH165" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -37453,6 +37973,9 @@
       <c r="BG166" t="n">
         <v>0</v>
       </c>
+      <c r="BH166" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -37634,6 +38157,9 @@
       <c r="BG167" t="n">
         <v>0</v>
       </c>
+      <c r="BH167" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -37810,9 +38336,12 @@
         <v>0</v>
       </c>
       <c r="BF168" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG168" t="n">
         <v>0.512</v>
       </c>
-      <c r="BG168" t="n">
+      <c r="BH168" t="n">
         <v>0</v>
       </c>
     </row>
@@ -37996,6 +38525,9 @@
       <c r="BG169" t="n">
         <v>0</v>
       </c>
+      <c r="BH169" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -38174,9 +38706,12 @@
         <v>0</v>
       </c>
       <c r="BF170" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG170" t="n">
         <v>-0.389</v>
       </c>
-      <c r="BG170" t="n">
+      <c r="BH170" t="n">
         <v>0</v>
       </c>
     </row>
@@ -38354,12 +38889,15 @@
         <v>0</v>
       </c>
       <c r="BE171" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF171" t="n">
         <v>-1.46</v>
       </c>
-      <c r="BF171" t="n">
+      <c r="BG171" t="n">
         <v>1.059</v>
       </c>
-      <c r="BG171" t="n">
+      <c r="BH171" t="n">
         <v>0</v>
       </c>
     </row>
@@ -38535,12 +39073,15 @@
         <v>0</v>
       </c>
       <c r="BE172" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF172" t="n">
         <v>0.765</v>
       </c>
-      <c r="BF172" t="n">
+      <c r="BG172" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BG172" t="n">
+      <c r="BH172" t="n">
         <v>0</v>
       </c>
     </row>
@@ -38719,9 +39260,12 @@
         <v>0</v>
       </c>
       <c r="BF173" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG173" t="n">
         <v>-0.389</v>
       </c>
-      <c r="BG173" t="n">
+      <c r="BH173" t="n">
         <v>0</v>
       </c>
     </row>
@@ -38902,9 +39446,12 @@
         <v>0</v>
       </c>
       <c r="BF174" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG174" t="n">
         <v>-0.047</v>
       </c>
-      <c r="BG174" t="n">
+      <c r="BH174" t="n">
         <v>0</v>
       </c>
     </row>
@@ -39085,9 +39632,12 @@
         <v>0</v>
       </c>
       <c r="BF175" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG175" t="n">
         <v>-0.011</v>
       </c>
-      <c r="BG175" t="n">
+      <c r="BH175" t="n">
         <v>0</v>
       </c>
     </row>
@@ -39273,6 +39823,9 @@
       <c r="BG176" t="n">
         <v>0</v>
       </c>
+      <c r="BH176" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -39454,6 +40007,9 @@
       <c r="BG177" t="n">
         <v>0</v>
       </c>
+      <c r="BH177" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -39637,6 +40193,9 @@
       <c r="BG178" t="n">
         <v>0</v>
       </c>
+      <c r="BH178" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -39820,6 +40379,9 @@
       <c r="BG179" t="n">
         <v>0</v>
       </c>
+      <c r="BH179" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -40003,6 +40565,9 @@
       <c r="BG180" t="n">
         <v>0</v>
       </c>
+      <c r="BH180" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -40182,6 +40747,9 @@
         <v>0</v>
       </c>
       <c r="BG181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH181" t="n">
         <v>0.424</v>
       </c>
     </row>
@@ -40363,6 +40931,9 @@
         <v>0</v>
       </c>
       <c r="BG182" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH182" t="n">
         <v>-0.141</v>
       </c>
     </row>
@@ -40544,6 +41115,9 @@
         <v>0</v>
       </c>
       <c r="BG183" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH183" t="n">
         <v>0.181</v>
       </c>
     </row>
@@ -40725,6 +41299,9 @@
         <v>0</v>
       </c>
       <c r="BG184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH184" t="n">
         <v>-0.271</v>
       </c>
     </row>
@@ -40906,6 +41483,9 @@
         <v>0</v>
       </c>
       <c r="BG185" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH185" t="n">
         <v>0.169</v>
       </c>
     </row>
@@ -41087,6 +41667,9 @@
         <v>0</v>
       </c>
       <c r="BG186" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH186" t="n">
         <v>-0.169</v>
       </c>
     </row>
@@ -41268,6 +41851,9 @@
         <v>0</v>
       </c>
       <c r="BG187" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH187" t="n">
         <v>0.113</v>
       </c>
     </row>
@@ -41449,6 +42035,9 @@
         <v>0</v>
       </c>
       <c r="BG188" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH188" t="n">
         <v>-0.113</v>
       </c>
     </row>
@@ -41630,6 +42219,9 @@
         <v>0</v>
       </c>
       <c r="BG189" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH189" t="n">
         <v>0.113</v>
       </c>
     </row>
@@ -41811,6 +42403,9 @@
         <v>0</v>
       </c>
       <c r="BG190" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH190" t="n">
         <v>-0.113</v>
       </c>
     </row>
@@ -41996,6 +42591,9 @@
       <c r="BG191" t="n">
         <v>0</v>
       </c>
+      <c r="BH191" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -42177,6 +42775,9 @@
       <c r="BG192" t="n">
         <v>0</v>
       </c>
+      <c r="BH192" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -42360,6 +42961,9 @@
       <c r="BG193" t="n">
         <v>0</v>
       </c>
+      <c r="BH193" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -42543,6 +43147,9 @@
       <c r="BG194" t="n">
         <v>0</v>
       </c>
+      <c r="BH194" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -42724,6 +43331,9 @@
       <c r="BG195" t="n">
         <v>0</v>
       </c>
+      <c r="BH195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -42905,6 +43515,9 @@
       <c r="BG196" t="n">
         <v>0</v>
       </c>
+      <c r="BH196" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -43086,6 +43699,9 @@
       <c r="BG197" t="n">
         <v>0</v>
       </c>
+      <c r="BH197" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -43267,6 +43883,9 @@
       <c r="BG198" t="n">
         <v>0</v>
       </c>
+      <c r="BH198" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -43448,6 +44067,9 @@
       <c r="BG199" t="n">
         <v>0</v>
       </c>
+      <c r="BH199" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -43629,6 +44251,9 @@
       <c r="BG200" t="n">
         <v>0</v>
       </c>
+      <c r="BH200" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -43810,6 +44435,9 @@
       <c r="BG201" t="n">
         <v>0</v>
       </c>
+      <c r="BH201" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -43991,6 +44619,9 @@
       <c r="BG202" t="n">
         <v>0</v>
       </c>
+      <c r="BH202" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -44172,6 +44803,9 @@
       <c r="BG203" t="n">
         <v>0</v>
       </c>
+      <c r="BH203" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -44353,6 +44987,9 @@
       <c r="BG204" t="n">
         <v>0</v>
       </c>
+      <c r="BH204" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -44534,9 +45171,12 @@
       <c r="BG205" t="n">
         <v>0</v>
       </c>
+      <c r="BH205" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:BG204">
+  <conditionalFormatting sqref="D2:BH204">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-1.5"/>
@@ -44558,7 +45198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G699"/>
+  <dimension ref="A1:G712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -52563,11 +53203,11 @@
     <row r="441">
       <c r="A441" s="12" t="inlineStr">
         <is>
-          <t>装机GWh / 最新储能装机</t>
+          <t>站内装机GWh / 最新储能装机</t>
         </is>
       </c>
       <c r="B441" s="13" t="n">
-        <v>107.94</v>
+        <v>6.29</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
@@ -52585,7 +53225,7 @@
         <v>351</v>
       </c>
       <c r="F442" s="4" t="n">
-        <v>-0.909</v>
+        <v>-0.906</v>
       </c>
       <c r="G442" t="inlineStr">
         <is>
@@ -52596,14 +53236,16 @@
     <row r="443">
       <c r="D443" t="inlineStr">
         <is>
-          <t>vehicles.private.scenes.0.swap_penetration</t>
-        </is>
-      </c>
-      <c r="E443" t="n">
-        <v>0</v>
+          <t>vehicles.heavy.nev_rates</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>[0.35, 0.43, 0.46, 0.48, 0.5]</t>
+        </is>
       </c>
       <c r="F443" s="4" t="n">
-        <v>0.764</v>
+        <v>0.652</v>
       </c>
       <c r="G443" t="inlineStr">
         <is>
@@ -52614,16 +53256,14 @@
     <row r="444">
       <c r="D444" t="inlineStr">
         <is>
-          <t>vehicles.heavy.nev_rates</t>
-        </is>
-      </c>
-      <c r="E444" t="inlineStr">
-        <is>
-          <t>[0.35, 0.43, 0.46, 0.48, 0.5]</t>
-        </is>
+          <t>stations.qiji75_trunk.inventory_blocks</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>24</v>
       </c>
       <c r="F444" s="4" t="n">
-        <v>0.467</v>
+        <v>0.62</v>
       </c>
       <c r="G444" t="inlineStr">
         <is>
@@ -52634,14 +53274,14 @@
     <row r="445">
       <c r="D445" t="inlineStr">
         <is>
-          <t>vehicles.heavy.scenes.1.swap_penetration</t>
+          <t>stations.qiji75_trunk.block_kwh</t>
         </is>
       </c>
       <c r="E445" t="n">
-        <v>0.5</v>
+        <v>171</v>
       </c>
       <c r="F445" s="4" t="n">
-        <v>0.23</v>
+        <v>0.62</v>
       </c>
       <c r="G445" t="inlineStr">
         <is>
@@ -52652,14 +53292,14 @@
     <row r="446">
       <c r="D446" t="inlineStr">
         <is>
-          <t>vehicles.heavy.scenes.1.catl_swap_share</t>
+          <t>vehicles.heavy.scenes.1.swap_penetration</t>
         </is>
       </c>
       <c r="E446" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F446" s="4" t="n">
-        <v>0.23</v>
+        <v>0.334</v>
       </c>
       <c r="G446" t="inlineStr">
         <is>
@@ -52670,16 +53310,14 @@
     <row r="447">
       <c r="D447" t="inlineStr">
         <is>
-          <t>vehicles.city.nev_rates</t>
-        </is>
-      </c>
-      <c r="E447" t="inlineStr">
-        <is>
-          <t>[0.5, 0.65, 0.8, 0.9, 0.95]</t>
-        </is>
+          <t>vehicles.heavy.scenes.1.catl_swap_share</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>0.3</v>
       </c>
       <c r="F447" s="4" t="n">
-        <v>0.184</v>
+        <v>0.334</v>
       </c>
       <c r="G447" t="inlineStr">
         <is>
@@ -52690,14 +53328,14 @@
     <row r="448">
       <c r="D448" t="inlineStr">
         <is>
-          <t>vehicles.city.scenes.0.swap_penetration</t>
+          <t>vehicles.heavy.scenes.2.swap_penetration</t>
         </is>
       </c>
       <c r="E448" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F448" s="4" t="n">
-        <v>0.184</v>
+        <v>0.27</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
@@ -52708,14 +53346,14 @@
     <row r="449">
       <c r="D449" t="inlineStr">
         <is>
-          <t>vehicles.city.scenes.0.catl_swap_share</t>
+          <t>vehicles.heavy.scenes.2.catl_swap_share</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F449" s="4" t="n">
-        <v>0.184</v>
+        <v>0.27</v>
       </c>
       <c r="G449" t="inlineStr">
         <is>
@@ -52726,14 +53364,16 @@
     <row r="450">
       <c r="D450" t="inlineStr">
         <is>
-          <t>vehicles.heavy.scenes.2.swap_penetration</t>
-        </is>
-      </c>
-      <c r="E450" t="n">
-        <v>0.7</v>
+          <t>vehicles.city.nev_rates</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>[0.5, 0.65, 0.8, 0.9, 0.95]</t>
+        </is>
       </c>
       <c r="F450" s="4" t="n">
-        <v>0.176</v>
+        <v>0.191</v>
       </c>
       <c r="G450" t="inlineStr">
         <is>
@@ -52744,14 +53384,14 @@
     <row r="451">
       <c r="D451" t="inlineStr">
         <is>
-          <t>vehicles.heavy.scenes.2.catl_swap_share</t>
+          <t>vehicles.city.scenes.0.swap_penetration</t>
         </is>
       </c>
       <c r="E451" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F451" s="4" t="n">
-        <v>0.176</v>
+        <v>0.191</v>
       </c>
       <c r="G451" t="inlineStr">
         <is>
@@ -52762,14 +53402,14 @@
     <row r="452">
       <c r="D452" t="inlineStr">
         <is>
-          <t>vehicles.private.scenes.1.swap_penetration</t>
+          <t>vehicles.city.scenes.0.catl_swap_share</t>
         </is>
       </c>
       <c r="E452" t="n">
-        <v>0.05</v>
+        <v>0.8</v>
       </c>
       <c r="F452" s="4" t="n">
-        <v>0.126</v>
+        <v>0.191</v>
       </c>
       <c r="G452" t="inlineStr">
         <is>
@@ -52780,14 +53420,14 @@
     <row r="453">
       <c r="D453" t="inlineStr">
         <is>
-          <t>vehicles.private.scenes.1.catl_swap_share</t>
+          <t>stations.choco35_city.inventory_blocks</t>
         </is>
       </c>
       <c r="E453" t="n">
-        <v>0.5</v>
+        <v>14</v>
       </c>
       <c r="F453" s="4" t="n">
-        <v>0.126</v>
+        <v>0.191</v>
       </c>
       <c r="G453" t="inlineStr">
         <is>
@@ -52798,11 +53438,11 @@
     <row r="454">
       <c r="A454" s="12" t="inlineStr">
         <is>
-          <t>装机GWh / 2030储能装机预测</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="B454" s="13" t="n">
-        <v>48.57</v>
+        <v>2.83</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
@@ -52820,7 +53460,7 @@
         <v>780</v>
       </c>
       <c r="F455" s="4" t="n">
-        <v>-0.908</v>
+        <v>-0.919</v>
       </c>
       <c r="G455" t="inlineStr">
         <is>
@@ -52831,14 +53471,16 @@
     <row r="456">
       <c r="D456" t="inlineStr">
         <is>
-          <t>vehicles.private.scenes.0.swap_penetration</t>
-        </is>
-      </c>
-      <c r="E456" t="n">
-        <v>0</v>
+          <t>vehicles.heavy.nev_rates</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>[0.35, 0.43, 0.46, 0.48, 0.5]</t>
+        </is>
       </c>
       <c r="F456" s="4" t="n">
-        <v>0.764</v>
+        <v>0.636</v>
       </c>
       <c r="G456" t="inlineStr">
         <is>
@@ -52849,16 +53491,14 @@
     <row r="457">
       <c r="D457" t="inlineStr">
         <is>
-          <t>vehicles.heavy.nev_rates</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>[0.35, 0.43, 0.46, 0.48, 0.5]</t>
-        </is>
+          <t>stations.qiji75_trunk.inventory_blocks</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>24</v>
       </c>
       <c r="F457" s="4" t="n">
-        <v>0.467</v>
+        <v>0.636</v>
       </c>
       <c r="G457" t="inlineStr">
         <is>
@@ -52869,14 +53509,14 @@
     <row r="458">
       <c r="D458" t="inlineStr">
         <is>
-          <t>vehicles.heavy.scenes.1.swap_penetration</t>
+          <t>stations.qiji75_trunk.block_kwh</t>
         </is>
       </c>
       <c r="E458" t="n">
-        <v>0.5</v>
+        <v>171</v>
       </c>
       <c r="F458" s="4" t="n">
-        <v>0.231</v>
+        <v>0.636</v>
       </c>
       <c r="G458" t="inlineStr">
         <is>
@@ -52887,14 +53527,14 @@
     <row r="459">
       <c r="D459" t="inlineStr">
         <is>
-          <t>vehicles.heavy.scenes.1.catl_swap_share</t>
+          <t>vehicles.heavy.scenes.1.swap_penetration</t>
         </is>
       </c>
       <c r="E459" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F459" s="4" t="n">
-        <v>0.231</v>
+        <v>0.318</v>
       </c>
       <c r="G459" t="inlineStr">
         <is>
@@ -52905,16 +53545,14 @@
     <row r="460">
       <c r="D460" t="inlineStr">
         <is>
-          <t>vehicles.city.nev_rates</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr">
-        <is>
-          <t>[0.5, 0.65, 0.8, 0.9, 0.95]</t>
-        </is>
+          <t>vehicles.heavy.scenes.1.catl_swap_share</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>0.3</v>
       </c>
       <c r="F460" s="4" t="n">
-        <v>0.185</v>
+        <v>0.318</v>
       </c>
       <c r="G460" t="inlineStr">
         <is>
@@ -52925,14 +53563,14 @@
     <row r="461">
       <c r="D461" t="inlineStr">
         <is>
-          <t>vehicles.city.scenes.0.swap_penetration</t>
+          <t>vehicles.heavy.scenes.2.swap_penetration</t>
         </is>
       </c>
       <c r="E461" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F461" s="4" t="n">
-        <v>0.185</v>
+        <v>0.283</v>
       </c>
       <c r="G461" t="inlineStr">
         <is>
@@ -52943,14 +53581,14 @@
     <row r="462">
       <c r="D462" t="inlineStr">
         <is>
-          <t>vehicles.city.scenes.0.catl_swap_share</t>
+          <t>vehicles.heavy.scenes.2.catl_swap_share</t>
         </is>
       </c>
       <c r="E462" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F462" s="4" t="n">
-        <v>0.185</v>
+        <v>0.283</v>
       </c>
       <c r="G462" t="inlineStr">
         <is>
@@ -52961,14 +53599,16 @@
     <row r="463">
       <c r="D463" t="inlineStr">
         <is>
-          <t>vehicles.heavy.scenes.2.swap_penetration</t>
-        </is>
-      </c>
-      <c r="E463" t="n">
-        <v>0.7</v>
+          <t>vehicles.city.nev_rates</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>[0.5, 0.65, 0.8, 0.9, 0.95]</t>
+        </is>
       </c>
       <c r="F463" s="4" t="n">
-        <v>0.177</v>
+        <v>0.212</v>
       </c>
       <c r="G463" t="inlineStr">
         <is>
@@ -52979,14 +53619,14 @@
     <row r="464">
       <c r="D464" t="inlineStr">
         <is>
-          <t>vehicles.heavy.scenes.2.catl_swap_share</t>
+          <t>vehicles.city.scenes.0.swap_penetration</t>
         </is>
       </c>
       <c r="E464" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F464" s="4" t="n">
-        <v>0.177</v>
+        <v>0.212</v>
       </c>
       <c r="G464" t="inlineStr">
         <is>
@@ -52997,14 +53637,14 @@
     <row r="465">
       <c r="D465" t="inlineStr">
         <is>
-          <t>vehicles.private.scenes.1.swap_penetration</t>
+          <t>vehicles.city.scenes.0.catl_swap_share</t>
         </is>
       </c>
       <c r="E465" t="n">
-        <v>0.05</v>
+        <v>0.8</v>
       </c>
       <c r="F465" s="4" t="n">
-        <v>0.126</v>
+        <v>0.212</v>
       </c>
       <c r="G465" t="inlineStr">
         <is>
@@ -53015,14 +53655,14 @@
     <row r="466">
       <c r="D466" t="inlineStr">
         <is>
-          <t>vehicles.private.scenes.1.catl_swap_share</t>
+          <t>stations.choco35_city.inventory_blocks</t>
         </is>
       </c>
       <c r="E466" t="n">
-        <v>0.5</v>
+        <v>14</v>
       </c>
       <c r="F466" s="4" t="n">
-        <v>0.126</v>
+        <v>0.212</v>
       </c>
       <c r="G466" t="inlineStr">
         <is>
@@ -56562,15 +57202,15 @@
     <row r="663">
       <c r="A663" s="12" t="inlineStr">
         <is>
-          <t>换电出资峰值/CFO</t>
+          <t>外部股权融资（合资方出资）</t>
         </is>
       </c>
       <c r="B663" s="13" t="n">
-        <v>0.08024040040331126</v>
+        <v>1031.349999241995</v>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>倍</t>
+          <t>亿元</t>
         </is>
       </c>
     </row>
@@ -56595,34 +57235,32 @@
     <row r="665">
       <c r="D665" t="inlineStr">
         <is>
-          <t>group_funding.projected_group_cfo_yi</t>
-        </is>
-      </c>
-      <c r="E665" t="inlineStr">
-        <is>
-          <t>[1450, 1600, 1800, 2000, 2250]</t>
-        </is>
+          <t>construction.battery_price_curve.platform_end_year</t>
+        </is>
+      </c>
+      <c r="E665" t="n">
+        <v>2028</v>
       </c>
       <c r="F665" s="4" t="n">
-        <v>-1.46</v>
+        <v>1.384</v>
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>↓反向</t>
+          <t>↑同向</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="D666" t="inlineStr">
         <is>
-          <t>finance.construction_ownership</t>
+          <t>construction.battery_price_curve.base_price_rmb_kwh</t>
         </is>
       </c>
       <c r="E666" t="n">
-        <v>0.4</v>
+        <v>590</v>
       </c>
       <c r="F666" s="4" t="n">
-        <v>1</v>
+        <v>0.922</v>
       </c>
       <c r="G666" t="inlineStr">
         <is>
@@ -56633,50 +57271,52 @@
     <row r="667">
       <c r="D667" t="inlineStr">
         <is>
-          <t>construction.battery_price_curve.base_price_rmb_kwh</t>
+          <t>finance.construction_ownership</t>
         </is>
       </c>
       <c r="E667" t="n">
-        <v>590</v>
+        <v>0.4</v>
       </c>
       <c r="F667" s="4" t="n">
-        <v>0.825</v>
+        <v>-0.667</v>
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>↑同向</t>
+          <t>↓反向</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="D668" t="inlineStr">
         <is>
-          <t>group_funding.reported_2026h1_cfo_yi</t>
+          <t>battery_life_model.critical_cycles</t>
         </is>
       </c>
       <c r="E668" t="n">
-        <v>602.17</v>
+        <v>2000</v>
       </c>
       <c r="F668" s="4" t="n">
-        <v>0.765</v>
+        <v>-0.629</v>
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>↑同向</t>
+          <t>↓反向</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="D669" t="inlineStr">
         <is>
-          <t>vehicles.private.scenes.0.swap_penetration</t>
-        </is>
-      </c>
-      <c r="E669" t="n">
-        <v>0</v>
+          <t>vehicles.heavy.nev_rates</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>[0.35, 0.43, 0.46, 0.48, 0.5]</t>
+        </is>
       </c>
       <c r="F669" s="4" t="n">
-        <v>0.573</v>
+        <v>0.577</v>
       </c>
       <c r="G669" t="inlineStr">
         <is>
@@ -56687,16 +57327,14 @@
     <row r="670">
       <c r="D670" t="inlineStr">
         <is>
-          <t>vehicles.heavy.nev_rates</t>
-        </is>
-      </c>
-      <c r="E670" t="inlineStr">
-        <is>
-          <t>[0.35, 0.43, 0.46, 0.48, 0.5]</t>
-        </is>
+          <t>vehicles.private.scenes.0.swap_penetration</t>
+        </is>
+      </c>
+      <c r="E670" t="n">
+        <v>0</v>
       </c>
       <c r="F670" s="4" t="n">
-        <v>0.39</v>
+        <v>0.422</v>
       </c>
       <c r="G670" t="inlineStr">
         <is>
@@ -56707,68 +57345,68 @@
     <row r="671">
       <c r="D671" t="inlineStr">
         <is>
-          <t>vehicles.heavy.scenes.1.swap_penetration</t>
+          <t>construction.battery_price_curve.storage_to_power_price_ratio</t>
         </is>
       </c>
       <c r="E671" t="n">
-        <v>0.5</v>
+        <v>0.917</v>
       </c>
       <c r="F671" s="4" t="n">
-        <v>0.188</v>
+        <v>-0.305</v>
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>↑同向</t>
+          <t>↓反向</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="D672" t="inlineStr">
         <is>
-          <t>vehicles.heavy.scenes.1.catl_swap_share</t>
+          <t>construction.battery_price_curve.retirement_soh</t>
         </is>
       </c>
       <c r="E672" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="F672" s="4" t="n">
-        <v>0.188</v>
+        <v>-0.305</v>
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>↑同向</t>
+          <t>↓反向</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="D673" t="inlineStr">
         <is>
-          <t>construction.station_2026_cumulative_targets.heavy</t>
+          <t>construction.battery_price_curve.secondary_market_discount</t>
         </is>
       </c>
       <c r="E673" t="n">
-        <v>1000</v>
+        <v>0.6</v>
       </c>
       <c r="F673" s="4" t="n">
-        <v>0.175</v>
+        <v>-0.305</v>
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>↑同向</t>
+          <t>↓反向</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="D674" t="inlineStr">
         <is>
-          <t>vehicles.heavy.scenes.2.swap_penetration</t>
+          <t>vehicles.heavy.scenes.1.swap_penetration</t>
         </is>
       </c>
       <c r="E674" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F674" s="4" t="n">
-        <v>0.148</v>
+        <v>0.272</v>
       </c>
       <c r="G674" t="inlineStr">
         <is>
@@ -56779,14 +57417,14 @@
     <row r="675">
       <c r="D675" t="inlineStr">
         <is>
-          <t>vehicles.heavy.scenes.2.catl_swap_share</t>
+          <t>vehicles.heavy.scenes.1.catl_swap_share</t>
         </is>
       </c>
       <c r="E675" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="F675" s="4" t="n">
-        <v>0.148</v>
+        <v>0.272</v>
       </c>
       <c r="G675" t="inlineStr">
         <is>
@@ -56797,105 +57435,103 @@
     <row r="676">
       <c r="A676" s="12" t="inlineStr">
         <is>
-          <t>2030期末可动用资金</t>
+          <t>换电出资峰值/CFO</t>
         </is>
       </c>
       <c r="B676" s="13" t="n">
-        <v>8593.75294231216</v>
+        <v>0.08024040040331126</v>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>亿元</t>
+          <t>倍</t>
         </is>
       </c>
     </row>
     <row r="677">
       <c r="D677" t="inlineStr">
         <is>
-          <t>group_funding.projected_group_cfo_yi</t>
-        </is>
-      </c>
-      <c r="E677" t="inlineStr">
-        <is>
-          <t>[1450, 1600, 1800, 2000, 2250]</t>
-        </is>
+          <t>finance.debt_ratio</t>
+        </is>
+      </c>
+      <c r="E677" t="n">
+        <v>0.6</v>
       </c>
       <c r="F677" s="4" t="n">
-        <v>1.059</v>
+        <v>-1.5</v>
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>↑同向</t>
+          <t>↓反向</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="D678" t="inlineStr">
         <is>
-          <t>group_funding.initial_cash_and_trading_assets_yi</t>
-        </is>
-      </c>
-      <c r="E678" t="n">
-        <v>4402.11</v>
+          <t>group_funding.projected_group_cfo_yi</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>[1450, 1600, 1800, 2000, 2250]</t>
+        </is>
       </c>
       <c r="F678" s="4" t="n">
-        <v>0.512</v>
+        <v>-1.46</v>
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>↑同向</t>
+          <t>↓反向</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="D679" t="inlineStr">
         <is>
-          <t>group_funding.projected_group_net_profit_yi</t>
-        </is>
-      </c>
-      <c r="E679" t="inlineStr">
-        <is>
-          <t>[1000, 1160, 1320, 1500, 1700]</t>
-        </is>
+          <t>finance.construction_ownership</t>
+        </is>
+      </c>
+      <c r="E679" t="n">
+        <v>0.4</v>
       </c>
       <c r="F679" s="4" t="n">
-        <v>-0.389</v>
+        <v>1</v>
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>↓反向</t>
+          <t>↑同向</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="D680" t="inlineStr">
         <is>
-          <t>group_funding.dividend_payout_ratio</t>
+          <t>construction.battery_price_curve.base_price_rmb_kwh</t>
         </is>
       </c>
       <c r="E680" t="n">
-        <v>0.5</v>
+        <v>590</v>
       </c>
       <c r="F680" s="4" t="n">
-        <v>-0.389</v>
+        <v>0.825</v>
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>↓反向</t>
+          <t>↑同向</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="D681" t="inlineStr">
         <is>
-          <t>finance.debt_ratio</t>
+          <t>group_funding.reported_2026h1_cfo_yi</t>
         </is>
       </c>
       <c r="E681" t="n">
-        <v>0.6</v>
+        <v>602.17</v>
       </c>
       <c r="F681" s="4" t="n">
-        <v>0.078</v>
+        <v>0.765</v>
       </c>
       <c r="G681" t="inlineStr">
         <is>
@@ -56906,141 +57542,139 @@
     <row r="682">
       <c r="D682" t="inlineStr">
         <is>
-          <t>group_funding.reported_2026h1_cfo_yi</t>
+          <t>vehicles.private.scenes.0.swap_penetration</t>
         </is>
       </c>
       <c r="E682" t="n">
-        <v>602.17</v>
+        <v>0</v>
       </c>
       <c r="F682" s="4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.573</v>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>↓反向</t>
+          <t>↑同向</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="D683" t="inlineStr">
         <is>
-          <t>finance.construction_ownership</t>
-        </is>
-      </c>
-      <c r="E683" t="n">
-        <v>0.4</v>
+          <t>vehicles.heavy.nev_rates</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>[0.35, 0.43, 0.46, 0.48, 0.5]</t>
+        </is>
       </c>
       <c r="F683" s="4" t="n">
-        <v>-0.052</v>
+        <v>0.39</v>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>↓反向</t>
+          <t>↑同向</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="D684" t="inlineStr">
         <is>
-          <t>group_funding.buyback_yi</t>
-        </is>
-      </c>
-      <c r="E684" t="inlineStr">
-        <is>
-          <t>[400, 0, 0, 0, 0]</t>
-        </is>
+          <t>vehicles.heavy.scenes.1.swap_penetration</t>
+        </is>
+      </c>
+      <c r="E684" t="n">
+        <v>0.5</v>
       </c>
       <c r="F684" s="4" t="n">
-        <v>-0.047</v>
+        <v>0.188</v>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>↓反向</t>
+          <t>↑同向</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="D685" t="inlineStr">
         <is>
-          <t>construction.battery_price_curve.base_price_rmb_kwh</t>
+          <t>vehicles.heavy.scenes.1.catl_swap_share</t>
         </is>
       </c>
       <c r="E685" t="n">
-        <v>590</v>
+        <v>0.3</v>
       </c>
       <c r="F685" s="4" t="n">
-        <v>-0.047</v>
+        <v>0.188</v>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>↓反向</t>
+          <t>↑同向</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="D686" t="inlineStr">
         <is>
-          <t>vehicles.private.scenes.0.swap_penetration</t>
+          <t>construction.station_2026_cumulative_targets.heavy</t>
         </is>
       </c>
       <c r="E686" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F686" s="4" t="n">
-        <v>-0.031</v>
+        <v>0.175</v>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>↓反向</t>
+          <t>↑同向</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="D687" t="inlineStr">
         <is>
-          <t>vehicles.heavy.nev_rates</t>
-        </is>
-      </c>
-      <c r="E687" t="inlineStr">
-        <is>
-          <t>[0.35, 0.43, 0.46, 0.48, 0.5]</t>
-        </is>
+          <t>vehicles.heavy.scenes.2.swap_penetration</t>
+        </is>
+      </c>
+      <c r="E687" t="n">
+        <v>0.7</v>
       </c>
       <c r="F687" s="4" t="n">
-        <v>-0.027</v>
+        <v>0.148</v>
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>↓反向</t>
+          <t>↑同向</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="D688" t="inlineStr">
         <is>
-          <t>construction.battery_price_curve.platform_end_year</t>
+          <t>vehicles.heavy.scenes.2.catl_swap_share</t>
         </is>
       </c>
       <c r="E688" t="n">
-        <v>2028</v>
+        <v>0.7</v>
       </c>
       <c r="F688" s="4" t="n">
-        <v>-0.015</v>
+        <v>0.148</v>
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>↓反向</t>
+          <t>↑同向</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" s="12" t="inlineStr">
         <is>
-          <t>待决战略敞口</t>
+          <t>2030期末可动用资金</t>
         </is>
       </c>
       <c r="B689" s="13" t="n">
-        <v>1770</v>
+        <v>8593.75294231216</v>
       </c>
       <c r="C689" t="inlineStr">
         <is>
@@ -57051,14 +57685,16 @@
     <row r="690">
       <c r="D690" t="inlineStr">
         <is>
-          <t>strategic_exposure.solid_state.full_newbuild_capex_yi</t>
-        </is>
-      </c>
-      <c r="E690" t="n">
-        <v>1000</v>
+          <t>group_funding.projected_group_cfo_yi</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>[1450, 1600, 1800, 2000, 2250]</t>
+        </is>
       </c>
       <c r="F690" s="4" t="n">
-        <v>0.424</v>
+        <v>1.059</v>
       </c>
       <c r="G690" t="inlineStr">
         <is>
@@ -57069,86 +57705,88 @@
     <row r="691">
       <c r="D691" t="inlineStr">
         <is>
-          <t>strategic_exposure.storage_aidc.assumed_reuse_rate</t>
+          <t>group_funding.initial_cash_and_trading_assets_yi</t>
         </is>
       </c>
       <c r="E691" t="n">
-        <v>0.6</v>
+        <v>4402.11</v>
       </c>
       <c r="F691" s="4" t="n">
-        <v>-0.271</v>
+        <v>0.512</v>
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>↓反向</t>
+          <t>↑同向</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="D692" t="inlineStr">
         <is>
-          <t>strategic_exposure.storage_aidc.full_newbuild_capex_yi</t>
-        </is>
-      </c>
-      <c r="E692" t="n">
-        <v>800</v>
+          <t>group_funding.projected_group_net_profit_yi</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>[1000, 1160, 1320, 1500, 1700]</t>
+        </is>
       </c>
       <c r="F692" s="4" t="n">
-        <v>0.181</v>
+        <v>-0.389</v>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>↑同向</t>
+          <t>↓反向</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="D693" t="inlineStr">
         <is>
-          <t>strategic_exposure.additional_mining.full_newbuild_capex_yi</t>
+          <t>group_funding.dividend_payout_ratio</t>
         </is>
       </c>
       <c r="E693" t="n">
-        <v>300</v>
+        <v>0.5</v>
       </c>
       <c r="F693" s="4" t="n">
-        <v>0.169</v>
+        <v>-0.389</v>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>↑同向</t>
+          <t>↓反向</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="D694" t="inlineStr">
         <is>
-          <t>strategic_exposure.additional_mining.assumed_reuse_rate</t>
+          <t>finance.debt_ratio</t>
         </is>
       </c>
       <c r="E694" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F694" s="4" t="n">
-        <v>-0.169</v>
+        <v>0.078</v>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>↓反向</t>
+          <t>↑同向</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="D695" t="inlineStr">
         <is>
-          <t>strategic_exposure.solid_state.assumed_reuse_rate</t>
+          <t>group_funding.reported_2026h1_cfo_yi</t>
         </is>
       </c>
       <c r="E695" t="n">
-        <v>0.25</v>
+        <v>602.17</v>
       </c>
       <c r="F695" s="4" t="n">
-        <v>-0.141</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G695" t="inlineStr">
         <is>
@@ -57159,32 +57797,34 @@
     <row r="696">
       <c r="D696" t="inlineStr">
         <is>
-          <t>strategic_exposure.software_ai.full_newbuild_capex_yi</t>
+          <t>finance.construction_ownership</t>
         </is>
       </c>
       <c r="E696" t="n">
-        <v>200</v>
+        <v>0.4</v>
       </c>
       <c r="F696" s="4" t="n">
-        <v>0.113</v>
+        <v>-0.052</v>
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>↑同向</t>
+          <t>↓反向</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="D697" t="inlineStr">
         <is>
-          <t>strategic_exposure.software_ai.assumed_reuse_rate</t>
-        </is>
-      </c>
-      <c r="E697" t="n">
-        <v>0</v>
+          <t>group_funding.buyback_yi</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>[400, 0, 0, 0, 0]</t>
+        </is>
       </c>
       <c r="F697" s="4" t="n">
-        <v>-0.113</v>
+        <v>-0.047</v>
       </c>
       <c r="G697" t="inlineStr">
         <is>
@@ -57195,34 +57835,267 @@
     <row r="698">
       <c r="D698" t="inlineStr">
         <is>
-          <t>strategic_exposure.cvc.full_newbuild_capex_yi</t>
+          <t>construction.battery_price_curve.base_price_rmb_kwh</t>
         </is>
       </c>
       <c r="E698" t="n">
-        <v>200</v>
+        <v>590</v>
       </c>
       <c r="F698" s="4" t="n">
-        <v>0.113</v>
+        <v>-0.047</v>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>↑同向</t>
+          <t>↓反向</t>
         </is>
       </c>
     </row>
     <row r="699">
       <c r="D699" t="inlineStr">
         <is>
+          <t>vehicles.private.scenes.0.swap_penetration</t>
+        </is>
+      </c>
+      <c r="E699" t="n">
+        <v>0</v>
+      </c>
+      <c r="F699" s="4" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>↓反向</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>vehicles.heavy.nev_rates</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>[0.35, 0.43, 0.46, 0.48, 0.5]</t>
+        </is>
+      </c>
+      <c r="F700" s="4" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>↓反向</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>construction.battery_price_curve.platform_end_year</t>
+        </is>
+      </c>
+      <c r="E701" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F701" s="4" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>↓反向</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="12" t="inlineStr">
+        <is>
+          <t>待决战略敞口</t>
+        </is>
+      </c>
+      <c r="B702" s="13" t="n">
+        <v>1770</v>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>亿元</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>strategic_exposure.solid_state.full_newbuild_capex_yi</t>
+        </is>
+      </c>
+      <c r="E703" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F703" s="4" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>↑同向</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>strategic_exposure.storage_aidc.assumed_reuse_rate</t>
+        </is>
+      </c>
+      <c r="E704" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F704" s="4" t="n">
+        <v>-0.271</v>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>↓反向</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>strategic_exposure.storage_aidc.full_newbuild_capex_yi</t>
+        </is>
+      </c>
+      <c r="E705" t="n">
+        <v>800</v>
+      </c>
+      <c r="F705" s="4" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>↑同向</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>strategic_exposure.additional_mining.full_newbuild_capex_yi</t>
+        </is>
+      </c>
+      <c r="E706" t="n">
+        <v>300</v>
+      </c>
+      <c r="F706" s="4" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>↑同向</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>strategic_exposure.additional_mining.assumed_reuse_rate</t>
+        </is>
+      </c>
+      <c r="E707" t="n">
+        <v>0</v>
+      </c>
+      <c r="F707" s="4" t="n">
+        <v>-0.169</v>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>↓反向</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>strategic_exposure.solid_state.assumed_reuse_rate</t>
+        </is>
+      </c>
+      <c r="E708" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F708" s="4" t="n">
+        <v>-0.141</v>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>↓反向</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>strategic_exposure.software_ai.full_newbuild_capex_yi</t>
+        </is>
+      </c>
+      <c r="E709" t="n">
+        <v>200</v>
+      </c>
+      <c r="F709" s="4" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>↑同向</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>strategic_exposure.software_ai.assumed_reuse_rate</t>
+        </is>
+      </c>
+      <c r="E710" t="n">
+        <v>0</v>
+      </c>
+      <c r="F710" s="4" t="n">
+        <v>-0.113</v>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>↓反向</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>strategic_exposure.cvc.full_newbuild_capex_yi</t>
+        </is>
+      </c>
+      <c r="E711" t="n">
+        <v>200</v>
+      </c>
+      <c r="F711" s="4" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>↑同向</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="D712" t="inlineStr">
+        <is>
           <t>strategic_exposure.cvc.assumed_reuse_rate</t>
         </is>
       </c>
-      <c r="E699" t="n">
-        <v>0</v>
-      </c>
-      <c r="F699" s="4" t="n">
+      <c r="E712" t="n">
+        <v>0</v>
+      </c>
+      <c r="F712" s="4" t="n">
         <v>-0.113</v>
       </c>
-      <c r="G699" t="inlineStr">
+      <c r="G712" t="inlineStr">
         <is>
           <t>↓反向</t>
         </is>
@@ -57926,37 +58799,37 @@
     <row r="53">
       <c r="C53" t="inlineStr">
         <is>
-          <t>换电装机保有量·站内周转</t>
+          <t>站内装机GWh / 最新储能装机</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>22.08291</v>
+        <v>6.29</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.643</v>
+        <v>0.652</v>
       </c>
     </row>
     <row r="54">
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">　服务费收入</t>
+          <t>换电装机保有量·站内周转</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>435.112608</v>
+        <v>22.08291</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.64</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="55">
       <c r="C55" t="inlineStr">
         <is>
-          <t>年换电交易电量</t>
+          <t xml:space="preserve">　服务费收入</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1450.37536</v>
+        <v>435.112608</v>
       </c>
       <c r="E55" s="4" t="n">
         <v>0.64</v>
@@ -57965,11 +58838,11 @@
     <row r="56">
       <c r="C56" t="inlineStr">
         <is>
-          <t>年换电量 / 最新年度全社会用电量</t>
+          <t>年换电交易电量</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1.3989</v>
+        <v>1450.37536</v>
       </c>
       <c r="E56" s="4" t="n">
         <v>0.64</v>
@@ -57978,66 +58851,66 @@
     <row r="57">
       <c r="C57" t="inlineStr">
         <is>
-          <t>年换电量 / 2030全社会用电量预测</t>
+          <t>年换电量 / 最新年度全社会用电量</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1.0744</v>
+        <v>1.3989</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.639</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="58">
       <c r="C58" t="inlineStr">
         <is>
-          <t>名义累计投入（不折现）</t>
+          <t>年换电量 / 2030全社会用电量预测</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5605.088897250862</v>
+        <v>1.0744</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.602</v>
+        <v>0.639</v>
       </c>
     </row>
     <row r="59">
       <c r="C59" t="inlineStr">
         <is>
-          <t>CATL归属·DCF有限期</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2023.880910498512</v>
+        <v>2.83</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.586</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="60">
       <c r="C60" t="inlineStr">
         <is>
-          <t>全周期资本底座（现值）</t>
+          <t>名义累计投入（不折现）</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4297.29166350831</v>
+        <v>5605.088897250862</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0.577</v>
+        <v>0.602</v>
       </c>
     </row>
     <row r="61">
       <c r="C61" t="inlineStr">
         <is>
-          <t>项目债务</t>
+          <t>CATL归属·DCF有限期</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2578.374998104986</v>
+        <v>2023.880910498512</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0.577</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="62">
@@ -58105,11 +58978,11 @@
     <row r="67">
       <c r="C67" t="inlineStr">
         <is>
-          <t>装机GWh / 最新储能装机</t>
+          <t>换电装机保有量·车端</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>107.94</v>
+        <v>378.8709285714285</v>
       </c>
       <c r="E67" s="4" t="n">
         <v>0.764</v>
@@ -58118,66 +58991,66 @@
     <row r="68">
       <c r="C68" t="inlineStr">
         <is>
-          <t>换电装机保有量·车端</t>
+          <t xml:space="preserve">　电池租金收入</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>378.8709285714285</v>
+        <v>470.5448094857143</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0.764</v>
+        <v>0.738</v>
       </c>
     </row>
     <row r="69">
       <c r="C69" t="inlineStr">
         <is>
-          <t>装机GWh / 2030储能装机预测</t>
+          <t>换电装机保有量合计</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>48.57</v>
+        <v>400.9538385714285</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>0.764</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="70">
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">　电池租金收入</t>
+          <t>峰值年权益出资</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>470.5448094857143</v>
+        <v>105.2510471325414</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>0.738</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="71">
       <c r="C71" t="inlineStr">
         <is>
-          <t>换电装机保有量合计</t>
+          <t>运营净利润（项目100%口径）</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>400.9538385714285</v>
+        <v>351.6165756151323</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>0.722</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="72">
       <c r="C72" t="inlineStr">
         <is>
-          <t>峰值年权益出资</t>
+          <t>运营净利润（CATL归属）</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>105.2510471325414</v>
+        <v>140.646630246053</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>0.655</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="73">
@@ -58232,24 +59105,24 @@
     <row r="77">
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">　服务费收入</t>
+          <t>站内装机GWh / 最新储能装机</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>435.112608</v>
+        <v>6.29</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>0.333</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="78">
       <c r="C78" t="inlineStr">
         <is>
-          <t>年换电交易电量</t>
+          <t xml:space="preserve">　服务费收入</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1450.37536</v>
+        <v>435.112608</v>
       </c>
       <c r="E78" s="4" t="n">
         <v>0.333</v>
@@ -58258,24 +59131,24 @@
     <row r="79">
       <c r="C79" t="inlineStr">
         <is>
-          <t>年换电量 / 最新年度全社会用电量</t>
+          <t>年换电交易电量</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1.3989</v>
+        <v>1450.37536</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>0.332</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="80">
       <c r="C80" t="inlineStr">
         <is>
-          <t>年换电量 / 2030全社会用电量预测</t>
+          <t>年换电量 / 最新年度全社会用电量</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1.0744</v>
+        <v>1.3989</v>
       </c>
       <c r="E80" s="4" t="n">
         <v>0.332</v>
@@ -58284,40 +59157,40 @@
     <row r="81">
       <c r="C81" t="inlineStr">
         <is>
-          <t>换电装机保有量·站内周转</t>
+          <t>年换电量 / 2030全社会用电量预测</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>22.08291</v>
+        <v>1.0744</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>0.325</v>
+        <v>0.332</v>
       </c>
     </row>
     <row r="82">
       <c r="C82" t="inlineStr">
         <is>
-          <t>增量价值/集团市值</t>
+          <t>换电装机保有量·站内周转</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.3051646059948464</v>
+        <v>22.08291</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>0.309</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="83">
       <c r="C83" t="inlineStr">
         <is>
-          <t>换电增量价值合计</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>6103.292119896928</v>
+        <v>2.83</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>0.309</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="84">
@@ -58359,24 +59232,24 @@
     <row r="87">
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">　服务费收入</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>435.112608</v>
+        <v>2.83</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>0.27</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="88">
       <c r="C88" t="inlineStr">
         <is>
-          <t>年换电交易电量</t>
+          <t xml:space="preserve">　服务费收入</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1450.37536</v>
+        <v>435.112608</v>
       </c>
       <c r="E88" s="4" t="n">
         <v>0.27</v>
@@ -58385,11 +59258,11 @@
     <row r="89">
       <c r="C89" t="inlineStr">
         <is>
-          <t>年换电量 / 最新年度全社会用电量</t>
+          <t>年换电交易电量</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1.3989</v>
+        <v>1450.37536</v>
       </c>
       <c r="E89" s="4" t="n">
         <v>0.27</v>
@@ -58398,11 +59271,11 @@
     <row r="90">
       <c r="C90" t="inlineStr">
         <is>
-          <t>年换电量 / 2030全社会用电量预测</t>
+          <t>站内装机GWh / 最新储能装机</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1.0744</v>
+        <v>6.29</v>
       </c>
       <c r="E90" s="4" t="n">
         <v>0.27</v>
@@ -58411,50 +59284,50 @@
     <row r="91">
       <c r="C91" t="inlineStr">
         <is>
-          <t>换电装机保有量·站内周转</t>
+          <t>年换电量 / 最新年度全社会用电量</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>22.08291</v>
+        <v>1.3989</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>0.264</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="92">
       <c r="C92" t="inlineStr">
         <is>
-          <t>名义累计投入（不折现）</t>
+          <t>年换电量 / 2030全社会用电量预测</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>5605.088897250862</v>
+        <v>1.0744</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>0.258</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="93">
       <c r="C93" t="inlineStr">
         <is>
-          <t>项目债务</t>
+          <t>换电装机保有量·站内周转</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2578.374998104986</v>
+        <v>22.08291</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>0.258</v>
+        <v>0.264</v>
       </c>
     </row>
     <row r="94">
       <c r="C94" t="inlineStr">
         <is>
-          <t>全周期资本底座（现值）</t>
+          <t>名义累计投入（不折现）</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>4297.29166350831</v>
+        <v>5605.088897250862</v>
       </c>
       <c r="E94" s="4" t="n">
         <v>0.258</v>
@@ -58486,24 +59359,24 @@
     <row r="97">
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">　服务费收入</t>
+          <t>站内装机GWh / 最新储能装机</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>435.112608</v>
+        <v>6.29</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>0.333</v>
+        <v>0.334</v>
       </c>
     </row>
     <row r="98">
       <c r="C98" t="inlineStr">
         <is>
-          <t>年换电交易电量</t>
+          <t xml:space="preserve">　服务费收入</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1450.37536</v>
+        <v>435.112608</v>
       </c>
       <c r="E98" s="4" t="n">
         <v>0.333</v>
@@ -58512,24 +59385,24 @@
     <row r="99">
       <c r="C99" t="inlineStr">
         <is>
-          <t>年换电量 / 最新年度全社会用电量</t>
+          <t>年换电交易电量</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1.3989</v>
+        <v>1450.37536</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>0.332</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="100">
       <c r="C100" t="inlineStr">
         <is>
-          <t>年换电量 / 2030全社会用电量预测</t>
+          <t>年换电量 / 最新年度全社会用电量</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1.0744</v>
+        <v>1.3989</v>
       </c>
       <c r="E100" s="4" t="n">
         <v>0.332</v>
@@ -58538,66 +59411,66 @@
     <row r="101">
       <c r="C101" t="inlineStr">
         <is>
-          <t>换电装机保有量·站内周转</t>
+          <t>年换电量 / 2030全社会用电量预测</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>22.08291</v>
+        <v>1.0744</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>0.325</v>
+        <v>0.332</v>
       </c>
     </row>
     <row r="102">
       <c r="C102" t="inlineStr">
         <is>
-          <t>名义累计投入（不折现）</t>
+          <t>换电装机保有量·站内周转</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>5605.088897250862</v>
+        <v>22.08291</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>0.303</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="103">
       <c r="C103" t="inlineStr">
         <is>
-          <t>CATL归属·DCF永续</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2088.73191426347</v>
+        <v>2.83</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>0.298</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="104">
       <c r="C104" t="inlineStr">
         <is>
-          <t>运营净利润（项目100%口径）</t>
+          <t>名义累计投入（不折现）</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>351.6165756151323</v>
+        <v>5605.088897250862</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>0.296</v>
+        <v>0.303</v>
       </c>
     </row>
     <row r="105">
       <c r="C105" t="inlineStr">
         <is>
-          <t>运营净利润（CATL归属）</t>
+          <t>CATL归属·DCF永续</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>140.646630246053</v>
+        <v>2088.73191426347</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>0.296</v>
+        <v>0.298</v>
       </c>
     </row>
     <row r="106">
@@ -58626,24 +59499,24 @@
     <row r="108">
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">　服务费收入</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>435.112608</v>
+        <v>2.83</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>0.27</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="109">
       <c r="C109" t="inlineStr">
         <is>
-          <t>年换电交易电量</t>
+          <t xml:space="preserve">　服务费收入</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1450.37536</v>
+        <v>435.112608</v>
       </c>
       <c r="E109" s="4" t="n">
         <v>0.27</v>
@@ -58652,11 +59525,11 @@
     <row r="110">
       <c r="C110" t="inlineStr">
         <is>
-          <t>年换电量 / 最新年度全社会用电量</t>
+          <t>年换电交易电量</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1.3989</v>
+        <v>1450.37536</v>
       </c>
       <c r="E110" s="4" t="n">
         <v>0.27</v>
@@ -58665,11 +59538,11 @@
     <row r="111">
       <c r="C111" t="inlineStr">
         <is>
-          <t>年换电量 / 2030全社会用电量预测</t>
+          <t>站内装机GWh / 最新储能装机</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1.0744</v>
+        <v>6.29</v>
       </c>
       <c r="E111" s="4" t="n">
         <v>0.27</v>
@@ -58678,50 +59551,50 @@
     <row r="112">
       <c r="C112" t="inlineStr">
         <is>
-          <t>换电装机保有量·站内周转</t>
+          <t>年换电量 / 最新年度全社会用电量</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>22.08291</v>
+        <v>1.3989</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>0.264</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="113">
       <c r="C113" t="inlineStr">
         <is>
-          <t>名义累计投入（不折现）</t>
+          <t>年换电量 / 2030全社会用电量预测</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>5605.088897250862</v>
+        <v>1.0744</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>0.258</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="114">
       <c r="C114" t="inlineStr">
         <is>
-          <t>项目债务</t>
+          <t>换电装机保有量·站内周转</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>2578.374998104986</v>
+        <v>22.08291</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>0.258</v>
+        <v>0.264</v>
       </c>
     </row>
     <row r="115">
       <c r="C115" t="inlineStr">
         <is>
-          <t>全周期资本底座（现值）</t>
+          <t>名义累计投入（不折现）</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>4297.29166350831</v>
+        <v>5605.088897250862</v>
       </c>
       <c r="E115" s="4" t="n">
         <v>0.258</v>
@@ -58730,14 +59603,14 @@
     <row r="116">
       <c r="C116" t="inlineStr">
         <is>
-          <t>CATL归属·DCF有限期</t>
+          <t>项目债务</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2023.880910498512</v>
+        <v>2578.374998104986</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>0.248</v>
+        <v>0.258</v>
       </c>
     </row>
     <row r="117">
@@ -58844,40 +59717,40 @@
     <row r="125">
       <c r="C125" t="inlineStr">
         <is>
-          <t>2030出货·换电车辆</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>107.230696969697</v>
+        <v>2.83</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>0.199</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="126">
       <c r="C126" t="inlineStr">
         <is>
-          <t>合并增量净利润</t>
+          <t>2030出货·换电车辆</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>170.9791750529392</v>
+        <v>107.230696969697</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>0.198</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="127">
       <c r="C127" t="inlineStr">
         <is>
-          <t>换电装机保有量·站内周转</t>
+          <t>合并增量净利润</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>22.08291</v>
+        <v>170.9791750529392</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>0.192</v>
+        <v>0.198</v>
       </c>
     </row>
     <row r="128">
@@ -58973,53 +59846,53 @@
     <row r="135">
       <c r="C135" t="inlineStr">
         <is>
-          <t>2030出货·换电车辆</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>107.230696969697</v>
+        <v>2.83</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>0.199</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="136">
       <c r="C136" t="inlineStr">
         <is>
-          <t>换电装机保有量·站内周转</t>
+          <t>2030出货·换电车辆</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>22.08291</v>
+        <v>107.230696969697</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>0.192</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="137">
       <c r="C137" t="inlineStr">
         <is>
-          <t>运营OPEX</t>
+          <t>换电装机保有量·站内周转</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>89.10089430972361</v>
+        <v>22.08291</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>0.19</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="138">
       <c r="C138" t="inlineStr">
         <is>
-          <t>终局初装CAPEX</t>
+          <t>站内装机GWh / 最新储能装机</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>2632.079559419369</v>
+        <v>6.29</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>0.189</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="139">
@@ -59113,53 +59986,53 @@
     <row r="146">
       <c r="C146" t="inlineStr">
         <is>
-          <t>2030出货·换电车辆</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>107.230696969697</v>
+        <v>2.83</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>0.199</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="147">
       <c r="C147" t="inlineStr">
         <is>
-          <t>换电装机保有量·站内周转</t>
+          <t>2030出货·换电车辆</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>22.08291</v>
+        <v>107.230696969697</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>0.192</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="148">
       <c r="C148" t="inlineStr">
         <is>
-          <t>运营OPEX</t>
+          <t>换电装机保有量·站内周转</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>89.10089430972361</v>
+        <v>22.08291</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>0.19</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="149">
       <c r="C149" t="inlineStr">
         <is>
-          <t>终局初装CAPEX</t>
+          <t>站内装机GWh / 最新储能装机</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>2632.079559419369</v>
+        <v>6.29</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>0.189</v>
+        <v>0.191</v>
       </c>
     </row>
     <row r="150">
@@ -59214,63 +60087,63 @@
     <row r="154">
       <c r="C154" t="inlineStr">
         <is>
-          <t>项目债务</t>
+          <t>外部股权融资（合资方出资）</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2578.374998104986</v>
+        <v>1031.349999241995</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>1</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="155">
       <c r="C155" t="inlineStr">
         <is>
-          <t>CATL归属·DCF有限期</t>
+          <t>项目债务</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>2023.880910498512</v>
+        <v>2578.374998104986</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>-0.309</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="C156" t="inlineStr">
         <is>
-          <t>CATL归属·DCF永续</t>
+          <t>CATL归属·DCF有限期</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>2088.73191426347</v>
+        <v>2023.880910498512</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>-0.3</v>
+        <v>-0.309</v>
       </c>
     </row>
     <row r="157">
       <c r="C157" t="inlineStr">
         <is>
-          <t>运营项目权益价值（100%口径）</t>
+          <t>CATL归属·DCF永续</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>13741.603059398</v>
+        <v>2088.73191426347</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>-0.114</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="158">
       <c r="C158" t="inlineStr">
         <is>
-          <t>运营权益价值(CATL归属)</t>
+          <t>运营项目权益价值（100%口径）</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>5496.641223759202</v>
+        <v>13741.603059398</v>
       </c>
       <c r="E158" s="4" t="n">
         <v>-0.114</v>
@@ -59279,27 +60152,27 @@
     <row r="159">
       <c r="C159" t="inlineStr">
         <is>
-          <t>合并增量价值（业务整体）</t>
+          <t>运营权益价值(CATL归属)</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>14348.25395553573</v>
+        <v>5496.641223759202</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>-0.109</v>
+        <v>-0.114</v>
       </c>
     </row>
     <row r="160">
       <c r="C160" t="inlineStr">
         <is>
-          <t>换电增量价值合计</t>
+          <t>合并增量价值（业务整体）</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>6103.292119896928</v>
+        <v>14348.25395553573</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>-0.103</v>
+        <v>-0.109</v>
       </c>
     </row>
     <row r="161">
@@ -59595,11 +60468,11 @@
     <row r="184">
       <c r="C184" t="inlineStr">
         <is>
-          <t>装机GWh / 最新储能装机</t>
+          <t>换电装机保有量·车端</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>107.94</v>
+        <v>378.8709285714285</v>
       </c>
       <c r="E184" s="4" t="n">
         <v>0.126</v>
@@ -59608,53 +60481,53 @@
     <row r="185">
       <c r="C185" t="inlineStr">
         <is>
-          <t>换电装机保有量·车端</t>
+          <t>合并增量净利润</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>378.8709285714285</v>
+        <v>170.9791750529392</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>0.126</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="186">
       <c r="C186" t="inlineStr">
         <is>
-          <t>装机GWh / 2030储能装机预测</t>
+          <t xml:space="preserve">　电池租金收入</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>48.57</v>
+        <v>470.5448094857143</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>0.126</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="187">
       <c r="C187" t="inlineStr">
         <is>
-          <t>合并增量净利润</t>
+          <t>换电装机保有量合计</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>170.9791750529392</v>
+        <v>400.9538385714285</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>0.123</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="188">
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">　电池租金收入</t>
+          <t>运营净利润（CATL归属）</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>470.5448094857143</v>
+        <v>140.646630246053</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>0.121</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="189">
@@ -59789,14 +60662,14 @@
     <row r="199">
       <c r="C199" t="inlineStr">
         <is>
-          <t>运营OPEX</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>89.10089430972361</v>
+        <v>2.83</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>0.102</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="200">
@@ -59864,11 +60737,11 @@
     <row r="205">
       <c r="C205" t="inlineStr">
         <is>
-          <t>装机GWh / 最新储能装机</t>
+          <t>换电装机保有量·车端</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>107.94</v>
+        <v>378.8709285714285</v>
       </c>
       <c r="E205" s="4" t="n">
         <v>0.126</v>
@@ -59877,63 +60750,63 @@
     <row r="206">
       <c r="C206" t="inlineStr">
         <is>
-          <t>换电装机保有量·车端</t>
+          <t xml:space="preserve">　电池租金收入</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>378.8709285714285</v>
+        <v>470.5448094857143</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>0.126</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="207">
       <c r="C207" t="inlineStr">
         <is>
-          <t>装机GWh / 2030储能装机预测</t>
+          <t>换电装机保有量合计</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>48.57</v>
+        <v>400.9538385714285</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>0.126</v>
+        <v>0.119</v>
       </c>
     </row>
     <row r="208">
       <c r="C208" t="inlineStr">
         <is>
-          <t xml:space="preserve">　电池租金收入</t>
+          <t>运营净利润（项目100%口径）</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>470.5448094857143</v>
+        <v>351.6165756151323</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>0.121</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="209">
       <c r="C209" t="inlineStr">
         <is>
-          <t>换电装机保有量合计</t>
+          <t>运营净利润（CATL归属）</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>400.9538385714285</v>
+        <v>140.646630246053</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>0.119</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="210">
       <c r="C210" t="inlineStr">
         <is>
-          <t>运营净利润（项目100%口径）</t>
+          <t>峰值年权益出资</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>351.6165756151323</v>
+        <v>105.2510471325414</v>
       </c>
       <c r="E210" s="4" t="n">
         <v>0.108</v>
@@ -60017,11 +60890,11 @@
     <row r="217">
       <c r="C217" t="inlineStr">
         <is>
-          <t>装机GWh / 最新储能装机</t>
+          <t>换电装机保有量·车端</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>107.94</v>
+        <v>378.8709285714285</v>
       </c>
       <c r="E217" s="4" t="n">
         <v>0.089</v>
@@ -60030,53 +60903,53 @@
     <row r="218">
       <c r="C218" t="inlineStr">
         <is>
-          <t>换电装机保有量·车端</t>
+          <t>合并增量净利润</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>378.8709285714285</v>
+        <v>170.9791750529392</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>0.089</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="219">
       <c r="C219" t="inlineStr">
         <is>
-          <t>装机GWh / 2030储能装机预测</t>
+          <t xml:space="preserve">　电池租金收入</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>48.57</v>
+        <v>470.5448094857143</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>0.089</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="220">
       <c r="C220" t="inlineStr">
         <is>
-          <t>合并增量净利润</t>
+          <t>换电装机保有量合计</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>170.9791750529392</v>
+        <v>400.9538385714285</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="221">
       <c r="C221" t="inlineStr">
         <is>
-          <t xml:space="preserve">　电池租金收入</t>
+          <t>运营净利润（CATL归属）</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>470.5448094857143</v>
+        <v>140.646630246053</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="222">
@@ -60297,24 +61170,24 @@
     <row r="239">
       <c r="C239" t="inlineStr">
         <is>
-          <t>峰值年权益出资</t>
+          <t>外部股权融资（合资方出资）</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>105.2510471325414</v>
+        <v>1031.349999241995</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>0.851</v>
+        <v>1.384</v>
       </c>
     </row>
     <row r="240">
       <c r="C240" t="inlineStr">
         <is>
-          <t>2030动力价值(无换电)</t>
+          <t>峰值年权益出资</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>8629.453108363636</v>
+        <v>105.2510471325414</v>
       </c>
       <c r="E240" s="4" t="n">
         <v>0.851</v>
@@ -60323,11 +61196,11 @@
     <row r="241">
       <c r="C241" t="inlineStr">
         <is>
-          <t>无换电制造净利</t>
+          <t>2030动力价值(无换电)</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>431.4726554181818</v>
+        <v>8629.453108363636</v>
       </c>
       <c r="E241" s="4" t="n">
         <v>0.851</v>
@@ -60336,11 +61209,11 @@
     <row r="242">
       <c r="C242" t="inlineStr">
         <is>
-          <t>有换电制造净利</t>
+          <t>无换电制造净利</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>461.8052002250681</v>
+        <v>431.4726554181818</v>
       </c>
       <c r="E242" s="4" t="n">
         <v>0.851</v>
@@ -60349,11 +61222,11 @@
     <row r="243">
       <c r="C243" t="inlineStr">
         <is>
-          <t>制造侧增量价值</t>
+          <t>有换电制造净利</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>606.6508961377258</v>
+        <v>461.8052002250681</v>
       </c>
       <c r="E243" s="4" t="n">
         <v>0.851</v>
@@ -60385,118 +61258,118 @@
     <row r="246">
       <c r="C246" t="inlineStr">
         <is>
-          <t>装机GWh / 2030储能装机预测</t>
+          <t>换电装机保有量·车端</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>48.57</v>
+        <v>378.8709285714285</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>0.074</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="247">
       <c r="C247" t="inlineStr">
         <is>
-          <t>装机GWh / 最新储能装机</t>
+          <t xml:space="preserve">　电池租金收入</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>107.94</v>
+        <v>470.5448094857143</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>0.073</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="248">
       <c r="C248" t="inlineStr">
         <is>
-          <t>换电装机保有量·车端</t>
+          <t>换电装机保有量合计</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>378.8709285714285</v>
+        <v>400.9538385714285</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>0.073</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="249">
       <c r="C249" t="inlineStr">
         <is>
-          <t xml:space="preserve">　电池租金收入</t>
+          <t>终局覆盖·商用营运车(重卡+城配)</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>470.5448094857143</v>
+        <v>123.5</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="250">
       <c r="C250" t="inlineStr">
         <is>
-          <t>换电装机保有量合计</t>
+          <t>终局初装CAPEX</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>400.9538385714285</v>
+        <v>2632.079559419369</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="251">
       <c r="C251" t="inlineStr">
         <is>
-          <t>终局覆盖·商用营运车(重卡+城配)</t>
+          <t>合并增量净利润</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>123.5</v>
+        <v>170.9791750529392</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>0.065</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="252">
       <c r="C252" t="inlineStr">
         <is>
-          <t>终局初装CAPEX</t>
+          <t>2030出货·换电装车</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>2632.079559419369</v>
+        <v>100.8568403030303</v>
       </c>
       <c r="E252" s="4" t="n">
-        <v>0.061</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="253">
       <c r="C253" t="inlineStr">
         <is>
-          <t>合并增量净利润</t>
+          <t>CATL权益出资合计</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>170.9791750529392</v>
+        <v>447.5955076878396</v>
       </c>
       <c r="E253" s="4" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="254">
       <c r="C254" t="inlineStr">
         <is>
-          <t>2030出货·换电装车</t>
+          <t>换电出资峰值/CFO</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>100.8568403030303</v>
+        <v>0.08024040040331126</v>
       </c>
       <c r="E254" s="4" t="n">
-        <v>0.058</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="255">
@@ -60603,24 +61476,24 @@
     <row r="263">
       <c r="C263" t="inlineStr">
         <is>
-          <t>终局初装CAPEX</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>2632.079559419369</v>
+        <v>2.83</v>
       </c>
       <c r="E263" s="4" t="n">
-        <v>0.064</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="264">
       <c r="C264" t="inlineStr">
         <is>
-          <t>运营OPEX</t>
+          <t>终局初装CAPEX</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>89.10089430972361</v>
+        <v>2632.079559419369</v>
       </c>
       <c r="E264" s="4" t="n">
         <v>0.064</v>
@@ -60629,14 +61502,14 @@
     <row r="265">
       <c r="C265" t="inlineStr">
         <is>
-          <t>装机GWh / 2030储能装机预测</t>
+          <t>站内装机GWh / 最新储能装机</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>48.57</v>
+        <v>6.29</v>
       </c>
       <c r="E265" s="4" t="n">
-        <v>0.062</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="266">
@@ -60704,11 +61577,11 @@
     <row r="271">
       <c r="C271" t="inlineStr">
         <is>
-          <t>装机GWh / 最新储能装机</t>
+          <t>换电装机保有量·车端</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>107.94</v>
+        <v>378.8709285714285</v>
       </c>
       <c r="E271" s="4" t="n">
         <v>0.089</v>
@@ -60717,63 +61590,63 @@
     <row r="272">
       <c r="C272" t="inlineStr">
         <is>
-          <t>换电装机保有量·车端</t>
+          <t xml:space="preserve">　电池租金收入</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>378.8709285714285</v>
+        <v>470.5448094857143</v>
       </c>
       <c r="E272" s="4" t="n">
-        <v>0.089</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="273">
       <c r="C273" t="inlineStr">
         <is>
-          <t>装机GWh / 2030储能装机预测</t>
+          <t>换电装机保有量合计</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>48.57</v>
+        <v>400.9538385714285</v>
       </c>
       <c r="E273" s="4" t="n">
-        <v>0.089</v>
+        <v>0.08400000000000001</v>
       </c>
     </row>
     <row r="274">
       <c r="C274" t="inlineStr">
         <is>
-          <t xml:space="preserve">　电池租金收入</t>
+          <t>运营净利润（CATL归属）</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>470.5448094857143</v>
+        <v>140.646630246053</v>
       </c>
       <c r="E274" s="4" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="275">
       <c r="C275" t="inlineStr">
         <is>
-          <t>换电装机保有量合计</t>
+          <t>运营净利润（项目100%口径）</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>400.9538385714285</v>
+        <v>351.6165756151323</v>
       </c>
       <c r="E275" s="4" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="276">
       <c r="C276" t="inlineStr">
         <is>
-          <t>运营净利润（CATL归属）</t>
+          <t>峰值年权益出资</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>140.646630246053</v>
+        <v>105.2510471325414</v>
       </c>
       <c r="E276" s="4" t="n">
         <v>0.076</v>
@@ -60818,11 +61691,11 @@
     <row r="280">
       <c r="C280" t="inlineStr">
         <is>
-          <t>项目债务</t>
+          <t>外部股权融资（合资方出资）</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>2578.374998104986</v>
+        <v>1031.349999241995</v>
       </c>
       <c r="E280" s="4" t="n">
         <v>-0.629</v>
@@ -60831,11 +61704,11 @@
     <row r="281">
       <c r="C281" t="inlineStr">
         <is>
-          <t>全周期资本底座（现值）</t>
+          <t>项目债务</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>4297.29166350831</v>
+        <v>2578.374998104986</v>
       </c>
       <c r="E281" s="4" t="n">
         <v>-0.629</v>
@@ -60844,37 +61717,37 @@
     <row r="282">
       <c r="C282" t="inlineStr">
         <is>
-          <t>资本回报要求EBITDA</t>
+          <t>全周期资本底座（现值）</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>745.3096780056391</v>
+        <v>4297.29166350831</v>
       </c>
       <c r="E282" s="4" t="n">
-        <v>-0.613</v>
+        <v>-0.629</v>
       </c>
     </row>
     <row r="283">
       <c r="C283" t="inlineStr">
         <is>
-          <t>运营净利润（项目100%口径）</t>
+          <t>资本回报要求EBITDA</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>351.6165756151323</v>
+        <v>745.3096780056391</v>
       </c>
       <c r="E283" s="4" t="n">
-        <v>0.53</v>
+        <v>-0.613</v>
       </c>
     </row>
     <row r="284">
       <c r="C284" t="inlineStr">
         <is>
-          <t>运营净利润（CATL归属）</t>
+          <t>运营净利润（项目100%口径）</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>140.646630246053</v>
+        <v>351.6165756151323</v>
       </c>
       <c r="E284" s="4" t="n">
         <v>0.53</v>
@@ -60883,40 +61756,40 @@
     <row r="285">
       <c r="C285" t="inlineStr">
         <is>
-          <t>合并增量净利润</t>
+          <t>运营净利润（CATL归属）</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>170.9791750529392</v>
+        <v>140.646630246053</v>
       </c>
       <c r="E285" s="4" t="n">
-        <v>0.382</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="286">
       <c r="C286" t="inlineStr">
         <is>
-          <t>制造侧增量价值</t>
+          <t>合并增量净利润</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>606.6508961377258</v>
+        <v>170.9791750529392</v>
       </c>
       <c r="E286" s="4" t="n">
-        <v>-0.308</v>
+        <v>0.382</v>
       </c>
     </row>
     <row r="287">
       <c r="C287" t="inlineStr">
         <is>
-          <t>CATL归属·DCF永续</t>
+          <t>制造侧增量价值</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>2088.73191426347</v>
+        <v>606.6508961377258</v>
       </c>
       <c r="E287" s="4" t="n">
-        <v>0.293</v>
+        <v>-0.308</v>
       </c>
     </row>
     <row r="288">
@@ -61212,131 +62085,131 @@
     <row r="311">
       <c r="C311" t="inlineStr">
         <is>
-          <t>换电装机保有量·站内周转</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>22.08291</v>
+        <v>2.83</v>
       </c>
       <c r="E311" s="4" t="n">
-        <v>0.616</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="312">
       <c r="C312" t="inlineStr">
         <is>
-          <t>运营净利润（项目100%口径）</t>
+          <t>站内装机GWh / 最新储能装机</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>351.6165756151323</v>
+        <v>6.29</v>
       </c>
       <c r="E312" s="4" t="n">
-        <v>0.054</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="313">
       <c r="C313" t="inlineStr">
         <is>
-          <t>运营净利润（CATL归属）</t>
+          <t>换电装机保有量·站内周转</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>140.646630246053</v>
+        <v>22.08291</v>
       </c>
       <c r="E313" s="4" t="n">
-        <v>0.054</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="314">
       <c r="C314" t="inlineStr">
         <is>
-          <t>CATL归属·DCF永续</t>
+          <t>运营净利润（项目100%口径）</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>2088.73191426347</v>
+        <v>351.6165756151323</v>
       </c>
       <c r="E314" s="4" t="n">
-        <v>0.044</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="315">
       <c r="C315" t="inlineStr">
         <is>
-          <t>合并增量净利润</t>
+          <t>运营净利润（CATL归属）</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>170.9791750529392</v>
+        <v>140.646630246053</v>
       </c>
       <c r="E315" s="4" t="n">
-        <v>0.043</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="316">
       <c r="C316" t="inlineStr">
         <is>
-          <t>DCF内在价值·永续EV</t>
+          <t>CATL归属·DCF永续</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>6787.688165568503</v>
+        <v>2088.73191426347</v>
       </c>
       <c r="E316" s="4" t="n">
-        <v>0.04</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="317">
       <c r="C317" t="inlineStr">
         <is>
-          <t>名义累计投入（不折现）</t>
+          <t>合并增量净利润</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>5605.088897250862</v>
+        <v>170.9791750529392</v>
       </c>
       <c r="E317" s="4" t="n">
-        <v>0.037</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="318">
       <c r="C318" t="inlineStr">
         <is>
-          <t>换电出资峰值/CFO</t>
+          <t>DCF内在价值·永续EV</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>0.08024040040331126</v>
+        <v>6787.688165568503</v>
       </c>
       <c r="E318" s="4" t="n">
-        <v>0.037</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="319">
       <c r="C319" t="inlineStr">
         <is>
-          <t>换电装机保有量合计</t>
+          <t>名义累计投入（不折现）</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>400.9538385714285</v>
+        <v>5605.088897250862</v>
       </c>
       <c r="E319" s="4" t="n">
-        <v>0.034</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="320">
       <c r="C320" t="inlineStr">
         <is>
-          <t>运营权益价值(CATL归属)</t>
+          <t>换电出资峰值/CFO</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>5496.641223759202</v>
+        <v>0.08024040040331126</v>
       </c>
       <c r="E320" s="4" t="n">
-        <v>0.032</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="321">
@@ -61352,131 +62225,131 @@
     <row r="322">
       <c r="C322" t="inlineStr">
         <is>
-          <t>换电装机保有量·站内周转</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>22.08291</v>
+        <v>2.83</v>
       </c>
       <c r="E322" s="4" t="n">
-        <v>0.616</v>
+        <v>0.636</v>
       </c>
     </row>
     <row r="323">
       <c r="C323" t="inlineStr">
         <is>
-          <t>运营净利润（项目100%口径）</t>
+          <t>站内装机GWh / 最新储能装机</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>351.6165756151323</v>
+        <v>6.29</v>
       </c>
       <c r="E323" s="4" t="n">
-        <v>0.054</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="324">
       <c r="C324" t="inlineStr">
         <is>
-          <t>运营净利润（CATL归属）</t>
+          <t>换电装机保有量·站内周转</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>140.646630246053</v>
+        <v>22.08291</v>
       </c>
       <c r="E324" s="4" t="n">
-        <v>0.054</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="325">
       <c r="C325" t="inlineStr">
         <is>
-          <t>CATL归属·DCF永续</t>
+          <t>运营净利润（项目100%口径）</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>2088.73191426347</v>
+        <v>351.6165756151323</v>
       </c>
       <c r="E325" s="4" t="n">
-        <v>0.044</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="326">
       <c r="C326" t="inlineStr">
         <is>
-          <t>合并增量净利润</t>
+          <t>运营净利润（CATL归属）</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>170.9791750529392</v>
+        <v>140.646630246053</v>
       </c>
       <c r="E326" s="4" t="n">
-        <v>0.043</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="327">
       <c r="C327" t="inlineStr">
         <is>
-          <t>DCF内在价值·永续EV</t>
+          <t>CATL归属·DCF永续</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>6787.688165568503</v>
+        <v>2088.73191426347</v>
       </c>
       <c r="E327" s="4" t="n">
-        <v>0.04</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="328">
       <c r="C328" t="inlineStr">
         <is>
-          <t>名义累计投入（不折现）</t>
+          <t>合并增量净利润</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>5605.088897250862</v>
+        <v>170.9791750529392</v>
       </c>
       <c r="E328" s="4" t="n">
-        <v>0.037</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="329">
       <c r="C329" t="inlineStr">
         <is>
-          <t>换电出资峰值/CFO</t>
+          <t>DCF内在价值·永续EV</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>0.08024040040331126</v>
+        <v>6787.688165568503</v>
       </c>
       <c r="E329" s="4" t="n">
-        <v>0.037</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="330">
       <c r="C330" t="inlineStr">
         <is>
-          <t>换电装机保有量合计</t>
+          <t>名义累计投入（不折现）</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>400.9538385714285</v>
+        <v>5605.088897250862</v>
       </c>
       <c r="E330" s="4" t="n">
-        <v>0.034</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="331">
       <c r="C331" t="inlineStr">
         <is>
-          <t>运营权益价值(CATL归属)</t>
+          <t>换电出资峰值/CFO</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>5496.641223759202</v>
+        <v>0.08024040040331126</v>
       </c>
       <c r="E331" s="4" t="n">
-        <v>0.032</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="332">
@@ -61596,27 +62469,27 @@
     <row r="341">
       <c r="C341" t="inlineStr">
         <is>
-          <t>制造侧增量价值</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>606.6508961377258</v>
+        <v>2.83</v>
       </c>
       <c r="E341" s="4" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="342">
       <c r="C342" t="inlineStr">
         <is>
-          <t>换电装机保有量·站内周转</t>
+          <t>制造侧增量价值</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>22.08291</v>
+        <v>606.6508961377258</v>
       </c>
       <c r="E342" s="4" t="n">
-        <v>0.032</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="343">
@@ -61738,27 +62611,27 @@
     <row r="352">
       <c r="C352" t="inlineStr">
         <is>
-          <t>换电装机保有量·站内周转</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>22.08291</v>
+        <v>2.83</v>
       </c>
       <c r="E352" s="4" t="n">
-        <v>0.032</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="353">
       <c r="C353" t="inlineStr">
         <is>
-          <t>终局初装CAPEX</t>
+          <t>换电装机保有量·站内周转</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>2632.079559419369</v>
+        <v>22.08291</v>
       </c>
       <c r="E353" s="4" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="354">
@@ -61878,27 +62751,27 @@
     <row r="363">
       <c r="C363" t="inlineStr">
         <is>
-          <t>换电装机保有量·站内周转</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>22.08291</v>
+        <v>2.83</v>
       </c>
       <c r="E363" s="4" t="n">
-        <v>0.032</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="364">
       <c r="C364" t="inlineStr">
         <is>
-          <t>终局初装CAPEX</t>
+          <t>换电装机保有量·站内周转</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>2632.079559419369</v>
+        <v>22.08291</v>
       </c>
       <c r="E364" s="4" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="365">
@@ -62018,27 +62891,27 @@
     <row r="374">
       <c r="C374" t="inlineStr">
         <is>
-          <t>换电装机保有量·站内周转</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>22.08291</v>
+        <v>2.83</v>
       </c>
       <c r="E374" s="4" t="n">
-        <v>0.032</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="375">
       <c r="C375" t="inlineStr">
         <is>
-          <t>终局初装CAPEX</t>
+          <t>换电装机保有量·站内周转</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>2632.079559419369</v>
+        <v>22.08291</v>
       </c>
       <c r="E375" s="4" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="376">
@@ -62132,11 +63005,11 @@
     <row r="383">
       <c r="C383" t="inlineStr">
         <is>
-          <t>2030出货·换电车辆</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>107.230696969697</v>
+        <v>2.83</v>
       </c>
       <c r="E383" s="4" t="n">
         <v>0.035</v>
@@ -62145,37 +63018,37 @@
     <row r="384">
       <c r="C384" t="inlineStr">
         <is>
-          <t>制造侧增量价值</t>
+          <t>2030出货·换电车辆</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>606.6508961377258</v>
+        <v>107.230696969697</v>
       </c>
       <c r="E384" s="4" t="n">
-        <v>0.031</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="385">
       <c r="C385" t="inlineStr">
         <is>
-          <t>终局初装CAPEX</t>
+          <t>制造侧增量价值</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>2632.079559419369</v>
+        <v>606.6508961377258</v>
       </c>
       <c r="E385" s="4" t="n">
-        <v>0.025</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="386">
       <c r="C386" t="inlineStr">
         <is>
-          <t>运营OPEX</t>
+          <t>终局初装CAPEX</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>89.10089430972361</v>
+        <v>2632.079559419369</v>
       </c>
       <c r="E386" s="4" t="n">
         <v>0.025</v>
@@ -62272,11 +63145,11 @@
     <row r="394">
       <c r="C394" t="inlineStr">
         <is>
-          <t>2030出货·换电车辆</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>107.230696969697</v>
+        <v>2.83</v>
       </c>
       <c r="E394" s="4" t="n">
         <v>-0.035</v>
@@ -62285,40 +63158,40 @@
     <row r="395">
       <c r="C395" t="inlineStr">
         <is>
-          <t>运营OPEX</t>
+          <t>2030出货·换电车辆</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>89.10089430972361</v>
+        <v>107.230696969697</v>
       </c>
       <c r="E395" s="4" t="n">
-        <v>-0.033</v>
+        <v>-0.035</v>
       </c>
     </row>
     <row r="396">
       <c r="C396" t="inlineStr">
         <is>
-          <t>换电装机保有量·站内周转</t>
+          <t>运营OPEX</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>22.08291</v>
+        <v>89.10089430972361</v>
       </c>
       <c r="E396" s="4" t="n">
-        <v>-0.028</v>
+        <v>-0.033</v>
       </c>
     </row>
     <row r="397">
       <c r="C397" t="inlineStr">
         <is>
-          <t>终局初装CAPEX</t>
+          <t>站内装机GWh / 最新储能装机</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>2632.079559419369</v>
+        <v>6.29</v>
       </c>
       <c r="E397" s="4" t="n">
-        <v>-0.027</v>
+        <v>-0.032</v>
       </c>
     </row>
     <row r="398">
@@ -62554,11 +63427,11 @@
     <row r="416">
       <c r="C416" t="inlineStr">
         <is>
-          <t>2030出货·换电车辆</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>107.230696969697</v>
+        <v>2.83</v>
       </c>
       <c r="E416" s="4" t="n">
         <v>0.035</v>
@@ -62567,24 +63440,24 @@
     <row r="417">
       <c r="C417" t="inlineStr">
         <is>
-          <t>终局初装CAPEX</t>
+          <t>2030出货·换电车辆</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>2632.079559419369</v>
+        <v>107.230696969697</v>
       </c>
       <c r="E417" s="4" t="n">
-        <v>0.025</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="418">
       <c r="C418" t="inlineStr">
         <is>
-          <t>运营OPEX</t>
+          <t>终局初装CAPEX</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>89.10089430972361</v>
+        <v>2632.079559419369</v>
       </c>
       <c r="E418" s="4" t="n">
         <v>0.025</v>
@@ -62593,11 +63466,11 @@
     <row r="419">
       <c r="C419" t="inlineStr">
         <is>
-          <t>装机GWh / 2030储能装机预测</t>
+          <t>运营OPEX</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>48.57</v>
+        <v>89.10089430972361</v>
       </c>
       <c r="E419" s="4" t="n">
         <v>0.025</v>
@@ -62694,11 +63567,11 @@
     <row r="427">
       <c r="C427" t="inlineStr">
         <is>
-          <t>2030出货·换电车辆</t>
+          <t>站内装机GWh / 2030储能装机预测</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>107.230696969697</v>
+        <v>2.83</v>
       </c>
       <c r="E427" s="4" t="n">
         <v>0.035</v>
@@ -62707,24 +63580,24 @@
     <row r="428">
       <c r="C428" t="inlineStr">
         <is>
-          <t>终局初装CAPEX</t>
+          <t>2030出货·换电车辆</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>2632.079559419369</v>
+        <v>107.230696969697</v>
       </c>
       <c r="E428" s="4" t="n">
-        <v>0.025</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="429">
       <c r="C429" t="inlineStr">
         <is>
-          <t>运营OPEX</t>
+          <t>终局初装CAPEX</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>89.10089430972361</v>
+        <v>2632.079559419369</v>
       </c>
       <c r="E429" s="4" t="n">
         <v>0.025</v>
@@ -62733,11 +63606,11 @@
     <row r="430">
       <c r="C430" t="inlineStr">
         <is>
-          <t>装机GWh / 2030储能装机预测</t>
+          <t>运营OPEX</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>48.57</v>
+        <v>89.10089430972361</v>
       </c>
       <c r="E430" s="4" t="n">
         <v>0.025</v>
